--- a/Chapters/Chapter 5 - Double Cloths/Double Cloths.xlsx
+++ b/Chapters/Chapter 5 - Double Cloths/Double Cloths.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Fabric Structure and Design (FSD)\Chapters\Chapter 5 - Double Cloths\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115E3F03-6E90-43D0-A883-76D75E213AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5606049B-B5B3-4E35-AB4E-CC8B6A330A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="769" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -158,12 +158,18 @@
   <si>
     <t>Stitching Point Center Weft Stitch With Back Warp</t>
   </si>
+  <si>
+    <t>FACE</t>
+  </si>
+  <si>
+    <t>BACK</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +186,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF7030A0"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Gill Sans MT"/>
       <family val="2"/>
     </font>
@@ -297,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -365,7 +378,16 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1907,115 +1929,115 @@
       </c>
     </row>
     <row r="36" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I36" s="23" t="s">
+      <c r="I36" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="S36" s="23" t="s">
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="S36" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="T36" s="23"/>
-      <c r="U36" s="23"/>
-      <c r="V36" s="23"/>
+      <c r="T36" s="24"/>
+      <c r="U36" s="24"/>
+      <c r="V36" s="24"/>
     </row>
     <row r="38" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB38" s="4"/>
-      <c r="AD38" s="23" t="s">
+      <c r="AD38" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="AE38" s="23"/>
-      <c r="AF38" s="23"/>
-      <c r="AG38" s="23"/>
-      <c r="AH38" s="23"/>
-      <c r="AI38" s="23"/>
-      <c r="AJ38" s="23"/>
-      <c r="AK38" s="23"/>
-      <c r="AL38" s="23"/>
-      <c r="AM38" s="23"/>
-      <c r="AN38" s="23"/>
-      <c r="AO38" s="23"/>
-      <c r="AP38" s="23"/>
-      <c r="AQ38" s="23"/>
+      <c r="AE38" s="24"/>
+      <c r="AF38" s="24"/>
+      <c r="AG38" s="24"/>
+      <c r="AH38" s="24"/>
+      <c r="AI38" s="24"/>
+      <c r="AJ38" s="24"/>
+      <c r="AK38" s="24"/>
+      <c r="AL38" s="24"/>
+      <c r="AM38" s="24"/>
+      <c r="AN38" s="24"/>
+      <c r="AO38" s="24"/>
+      <c r="AP38" s="24"/>
+      <c r="AQ38" s="24"/>
     </row>
     <row r="40" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB40" s="5"/>
-      <c r="AD40" s="23" t="s">
+      <c r="AD40" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="AE40" s="23"/>
-      <c r="AF40" s="23"/>
-      <c r="AG40" s="23"/>
-      <c r="AH40" s="23"/>
-      <c r="AI40" s="23"/>
-      <c r="AJ40" s="23"/>
-      <c r="AK40" s="23"/>
-      <c r="AL40" s="23"/>
-      <c r="AM40" s="23"/>
-      <c r="AN40" s="23"/>
-      <c r="AO40" s="23"/>
-      <c r="AP40" s="23"/>
-      <c r="AQ40" s="23"/>
+      <c r="AE40" s="24"/>
+      <c r="AF40" s="24"/>
+      <c r="AG40" s="24"/>
+      <c r="AH40" s="24"/>
+      <c r="AI40" s="24"/>
+      <c r="AJ40" s="24"/>
+      <c r="AK40" s="24"/>
+      <c r="AL40" s="24"/>
+      <c r="AM40" s="24"/>
+      <c r="AN40" s="24"/>
+      <c r="AO40" s="24"/>
+      <c r="AP40" s="24"/>
+      <c r="AQ40" s="24"/>
     </row>
     <row r="42" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB42" s="7"/>
-      <c r="AD42" s="23" t="s">
+      <c r="AD42" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AE42" s="23"/>
-      <c r="AF42" s="23"/>
-      <c r="AG42" s="23"/>
-      <c r="AH42" s="23"/>
-      <c r="AI42" s="23"/>
-      <c r="AJ42" s="23"/>
-      <c r="AK42" s="23"/>
-      <c r="AL42" s="23"/>
-      <c r="AM42" s="23"/>
-      <c r="AN42" s="23"/>
-      <c r="AO42" s="23"/>
-      <c r="AP42" s="23"/>
-      <c r="AQ42" s="23"/>
+      <c r="AE42" s="24"/>
+      <c r="AF42" s="24"/>
+      <c r="AG42" s="24"/>
+      <c r="AH42" s="24"/>
+      <c r="AI42" s="24"/>
+      <c r="AJ42" s="24"/>
+      <c r="AK42" s="24"/>
+      <c r="AL42" s="24"/>
+      <c r="AM42" s="24"/>
+      <c r="AN42" s="24"/>
+      <c r="AO42" s="24"/>
+      <c r="AP42" s="24"/>
+      <c r="AQ42" s="24"/>
     </row>
     <row r="44" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB44" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AD44" s="23" t="s">
+      <c r="AD44" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="AE44" s="23"/>
-      <c r="AF44" s="23"/>
-      <c r="AG44" s="23"/>
-      <c r="AH44" s="23"/>
-      <c r="AI44" s="23"/>
-      <c r="AJ44" s="23"/>
-      <c r="AK44" s="23"/>
-      <c r="AL44" s="23"/>
-      <c r="AM44" s="23"/>
-      <c r="AN44" s="23"/>
-      <c r="AO44" s="23"/>
-      <c r="AP44" s="23"/>
-      <c r="AQ44" s="23"/>
+      <c r="AE44" s="24"/>
+      <c r="AF44" s="24"/>
+      <c r="AG44" s="24"/>
+      <c r="AH44" s="24"/>
+      <c r="AI44" s="24"/>
+      <c r="AJ44" s="24"/>
+      <c r="AK44" s="24"/>
+      <c r="AL44" s="24"/>
+      <c r="AM44" s="24"/>
+      <c r="AN44" s="24"/>
+      <c r="AO44" s="24"/>
+      <c r="AP44" s="24"/>
+      <c r="AQ44" s="24"/>
     </row>
     <row r="46" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB46" s="3"/>
-      <c r="AD46" s="23" t="s">
+      <c r="AD46" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="AE46" s="23"/>
-      <c r="AF46" s="23"/>
-      <c r="AG46" s="23"/>
-      <c r="AH46" s="23"/>
-      <c r="AI46" s="23"/>
-      <c r="AJ46" s="23"/>
-      <c r="AK46" s="23"/>
-      <c r="AL46" s="23"/>
-      <c r="AM46" s="23"/>
-      <c r="AN46" s="23"/>
-      <c r="AO46" s="23"/>
-      <c r="AP46" s="23"/>
-      <c r="AQ46" s="23"/>
+      <c r="AE46" s="24"/>
+      <c r="AF46" s="24"/>
+      <c r="AG46" s="24"/>
+      <c r="AH46" s="24"/>
+      <c r="AI46" s="24"/>
+      <c r="AJ46" s="24"/>
+      <c r="AK46" s="24"/>
+      <c r="AL46" s="24"/>
+      <c r="AM46" s="24"/>
+      <c r="AN46" s="24"/>
+      <c r="AO46" s="24"/>
+      <c r="AP46" s="24"/>
+      <c r="AQ46" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3287,115 +3309,115 @@
       </c>
     </row>
     <row r="36" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I36" s="23" t="s">
+      <c r="I36" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="S36" s="23" t="s">
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="S36" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="T36" s="23"/>
-      <c r="U36" s="23"/>
-      <c r="V36" s="23"/>
+      <c r="T36" s="24"/>
+      <c r="U36" s="24"/>
+      <c r="V36" s="24"/>
     </row>
     <row r="38" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB38" s="4"/>
-      <c r="AD38" s="23" t="s">
+      <c r="AD38" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="AE38" s="23"/>
-      <c r="AF38" s="23"/>
-      <c r="AG38" s="23"/>
-      <c r="AH38" s="23"/>
-      <c r="AI38" s="23"/>
-      <c r="AJ38" s="23"/>
-      <c r="AK38" s="23"/>
-      <c r="AL38" s="23"/>
-      <c r="AM38" s="23"/>
-      <c r="AN38" s="23"/>
-      <c r="AO38" s="23"/>
-      <c r="AP38" s="23"/>
-      <c r="AQ38" s="23"/>
+      <c r="AE38" s="24"/>
+      <c r="AF38" s="24"/>
+      <c r="AG38" s="24"/>
+      <c r="AH38" s="24"/>
+      <c r="AI38" s="24"/>
+      <c r="AJ38" s="24"/>
+      <c r="AK38" s="24"/>
+      <c r="AL38" s="24"/>
+      <c r="AM38" s="24"/>
+      <c r="AN38" s="24"/>
+      <c r="AO38" s="24"/>
+      <c r="AP38" s="24"/>
+      <c r="AQ38" s="24"/>
     </row>
     <row r="40" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB40" s="5"/>
-      <c r="AD40" s="23" t="s">
+      <c r="AD40" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="AE40" s="23"/>
-      <c r="AF40" s="23"/>
-      <c r="AG40" s="23"/>
-      <c r="AH40" s="23"/>
-      <c r="AI40" s="23"/>
-      <c r="AJ40" s="23"/>
-      <c r="AK40" s="23"/>
-      <c r="AL40" s="23"/>
-      <c r="AM40" s="23"/>
-      <c r="AN40" s="23"/>
-      <c r="AO40" s="23"/>
-      <c r="AP40" s="23"/>
-      <c r="AQ40" s="23"/>
+      <c r="AE40" s="24"/>
+      <c r="AF40" s="24"/>
+      <c r="AG40" s="24"/>
+      <c r="AH40" s="24"/>
+      <c r="AI40" s="24"/>
+      <c r="AJ40" s="24"/>
+      <c r="AK40" s="24"/>
+      <c r="AL40" s="24"/>
+      <c r="AM40" s="24"/>
+      <c r="AN40" s="24"/>
+      <c r="AO40" s="24"/>
+      <c r="AP40" s="24"/>
+      <c r="AQ40" s="24"/>
     </row>
     <row r="42" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB42" s="6"/>
-      <c r="AD42" s="23" t="s">
+      <c r="AD42" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AE42" s="23"/>
-      <c r="AF42" s="23"/>
-      <c r="AG42" s="23"/>
-      <c r="AH42" s="23"/>
-      <c r="AI42" s="23"/>
-      <c r="AJ42" s="23"/>
-      <c r="AK42" s="23"/>
-      <c r="AL42" s="23"/>
-      <c r="AM42" s="23"/>
-      <c r="AN42" s="23"/>
-      <c r="AO42" s="23"/>
-      <c r="AP42" s="23"/>
-      <c r="AQ42" s="23"/>
+      <c r="AE42" s="24"/>
+      <c r="AF42" s="24"/>
+      <c r="AG42" s="24"/>
+      <c r="AH42" s="24"/>
+      <c r="AI42" s="24"/>
+      <c r="AJ42" s="24"/>
+      <c r="AK42" s="24"/>
+      <c r="AL42" s="24"/>
+      <c r="AM42" s="24"/>
+      <c r="AN42" s="24"/>
+      <c r="AO42" s="24"/>
+      <c r="AP42" s="24"/>
+      <c r="AQ42" s="24"/>
     </row>
     <row r="44" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB44" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AD44" s="23" t="s">
+      <c r="AD44" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="AE44" s="23"/>
-      <c r="AF44" s="23"/>
-      <c r="AG44" s="23"/>
-      <c r="AH44" s="23"/>
-      <c r="AI44" s="23"/>
-      <c r="AJ44" s="23"/>
-      <c r="AK44" s="23"/>
-      <c r="AL44" s="23"/>
-      <c r="AM44" s="23"/>
-      <c r="AN44" s="23"/>
-      <c r="AO44" s="23"/>
-      <c r="AP44" s="23"/>
-      <c r="AQ44" s="23"/>
+      <c r="AE44" s="24"/>
+      <c r="AF44" s="24"/>
+      <c r="AG44" s="24"/>
+      <c r="AH44" s="24"/>
+      <c r="AI44" s="24"/>
+      <c r="AJ44" s="24"/>
+      <c r="AK44" s="24"/>
+      <c r="AL44" s="24"/>
+      <c r="AM44" s="24"/>
+      <c r="AN44" s="24"/>
+      <c r="AO44" s="24"/>
+      <c r="AP44" s="24"/>
+      <c r="AQ44" s="24"/>
     </row>
     <row r="46" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB46" s="3"/>
-      <c r="AD46" s="23" t="s">
+      <c r="AD46" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="AE46" s="23"/>
-      <c r="AF46" s="23"/>
-      <c r="AG46" s="23"/>
-      <c r="AH46" s="23"/>
-      <c r="AI46" s="23"/>
-      <c r="AJ46" s="23"/>
-      <c r="AK46" s="23"/>
-      <c r="AL46" s="23"/>
-      <c r="AM46" s="23"/>
-      <c r="AN46" s="23"/>
-      <c r="AO46" s="23"/>
-      <c r="AP46" s="23"/>
-      <c r="AQ46" s="23"/>
+      <c r="AE46" s="24"/>
+      <c r="AF46" s="24"/>
+      <c r="AG46" s="24"/>
+      <c r="AH46" s="24"/>
+      <c r="AI46" s="24"/>
+      <c r="AJ46" s="24"/>
+      <c r="AK46" s="24"/>
+      <c r="AL46" s="24"/>
+      <c r="AM46" s="24"/>
+      <c r="AN46" s="24"/>
+      <c r="AO46" s="24"/>
+      <c r="AP46" s="24"/>
+      <c r="AQ46" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3414,7 +3436,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF454447-F027-4CC3-B90F-BF03BCB9277B}">
-  <dimension ref="F2:BH46"/>
+  <dimension ref="F2:BU86"/>
   <sheetFormatPr defaultColWidth="3.5546875" defaultRowHeight="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="26" width="3.5546875" style="2"/>
@@ -4699,118 +4721,1269 @@
       </c>
     </row>
     <row r="36" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I36" s="23" t="s">
+      <c r="I36" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="S36" s="23" t="s">
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="S36" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="T36" s="23"/>
-      <c r="U36" s="23"/>
-      <c r="V36" s="23"/>
+      <c r="T36" s="24"/>
+      <c r="U36" s="24"/>
+      <c r="V36" s="24"/>
     </row>
     <row r="38" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB38" s="4"/>
-      <c r="AD38" s="23" t="s">
+      <c r="AD38" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="AE38" s="23"/>
-      <c r="AF38" s="23"/>
-      <c r="AG38" s="23"/>
-      <c r="AH38" s="23"/>
-      <c r="AI38" s="23"/>
-      <c r="AJ38" s="23"/>
-      <c r="AK38" s="23"/>
-      <c r="AL38" s="23"/>
-      <c r="AM38" s="23"/>
-      <c r="AN38" s="23"/>
-      <c r="AO38" s="23"/>
-      <c r="AP38" s="23"/>
-      <c r="AQ38" s="23"/>
+      <c r="AE38" s="24"/>
+      <c r="AF38" s="24"/>
+      <c r="AG38" s="24"/>
+      <c r="AH38" s="24"/>
+      <c r="AI38" s="24"/>
+      <c r="AJ38" s="24"/>
+      <c r="AK38" s="24"/>
+      <c r="AL38" s="24"/>
+      <c r="AM38" s="24"/>
+      <c r="AN38" s="24"/>
+      <c r="AO38" s="24"/>
+      <c r="AP38" s="24"/>
+      <c r="AQ38" s="24"/>
     </row>
     <row r="40" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB40" s="5"/>
-      <c r="AD40" s="23" t="s">
+      <c r="AD40" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="AE40" s="23"/>
-      <c r="AF40" s="23"/>
-      <c r="AG40" s="23"/>
-      <c r="AH40" s="23"/>
-      <c r="AI40" s="23"/>
-      <c r="AJ40" s="23"/>
-      <c r="AK40" s="23"/>
-      <c r="AL40" s="23"/>
-      <c r="AM40" s="23"/>
-      <c r="AN40" s="23"/>
-      <c r="AO40" s="23"/>
-      <c r="AP40" s="23"/>
-      <c r="AQ40" s="23"/>
+      <c r="AE40" s="24"/>
+      <c r="AF40" s="24"/>
+      <c r="AG40" s="24"/>
+      <c r="AH40" s="24"/>
+      <c r="AI40" s="24"/>
+      <c r="AJ40" s="24"/>
+      <c r="AK40" s="24"/>
+      <c r="AL40" s="24"/>
+      <c r="AM40" s="24"/>
+      <c r="AN40" s="24"/>
+      <c r="AO40" s="24"/>
+      <c r="AP40" s="24"/>
+      <c r="AQ40" s="24"/>
     </row>
     <row r="42" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB42" s="6"/>
-      <c r="AD42" s="23" t="s">
+      <c r="AD42" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AE42" s="23"/>
-      <c r="AF42" s="23"/>
-      <c r="AG42" s="23"/>
-      <c r="AH42" s="23"/>
-      <c r="AI42" s="23"/>
-      <c r="AJ42" s="23"/>
-      <c r="AK42" s="23"/>
-      <c r="AL42" s="23"/>
-      <c r="AM42" s="23"/>
-      <c r="AN42" s="23"/>
-      <c r="AO42" s="23"/>
-      <c r="AP42" s="23"/>
-      <c r="AQ42" s="23"/>
+      <c r="AE42" s="24"/>
+      <c r="AF42" s="24"/>
+      <c r="AG42" s="24"/>
+      <c r="AH42" s="24"/>
+      <c r="AI42" s="24"/>
+      <c r="AJ42" s="24"/>
+      <c r="AK42" s="24"/>
+      <c r="AL42" s="24"/>
+      <c r="AM42" s="24"/>
+      <c r="AN42" s="24"/>
+      <c r="AO42" s="24"/>
+      <c r="AP42" s="24"/>
+      <c r="AQ42" s="24"/>
     </row>
     <row r="44" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB44" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AD44" s="23" t="s">
+      <c r="AD44" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="AE44" s="23"/>
-      <c r="AF44" s="23"/>
-      <c r="AG44" s="23"/>
-      <c r="AH44" s="23"/>
-      <c r="AI44" s="23"/>
-      <c r="AJ44" s="23"/>
-      <c r="AK44" s="23"/>
-      <c r="AL44" s="23"/>
-      <c r="AM44" s="23"/>
-      <c r="AN44" s="23"/>
-      <c r="AO44" s="23"/>
-      <c r="AP44" s="23"/>
-      <c r="AQ44" s="23"/>
+      <c r="AE44" s="24"/>
+      <c r="AF44" s="24"/>
+      <c r="AG44" s="24"/>
+      <c r="AH44" s="24"/>
+      <c r="AI44" s="24"/>
+      <c r="AJ44" s="24"/>
+      <c r="AK44" s="24"/>
+      <c r="AL44" s="24"/>
+      <c r="AM44" s="24"/>
+      <c r="AN44" s="24"/>
+      <c r="AO44" s="24"/>
+      <c r="AP44" s="24"/>
+      <c r="AQ44" s="24"/>
     </row>
     <row r="46" spans="6:60" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB46" s="3"/>
-      <c r="AD46" s="23" t="s">
+      <c r="AD46" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="AE46" s="23"/>
-      <c r="AF46" s="23"/>
-      <c r="AG46" s="23"/>
-      <c r="AH46" s="23"/>
-      <c r="AI46" s="23"/>
-      <c r="AJ46" s="23"/>
-      <c r="AK46" s="23"/>
-      <c r="AL46" s="23"/>
-      <c r="AM46" s="23"/>
-      <c r="AN46" s="23"/>
-      <c r="AO46" s="23"/>
-      <c r="AP46" s="23"/>
-      <c r="AQ46" s="23"/>
+      <c r="AE46" s="24"/>
+      <c r="AF46" s="24"/>
+      <c r="AG46" s="24"/>
+      <c r="AH46" s="24"/>
+      <c r="AI46" s="24"/>
+      <c r="AJ46" s="24"/>
+      <c r="AK46" s="24"/>
+      <c r="AL46" s="24"/>
+      <c r="AM46" s="24"/>
+      <c r="AN46" s="24"/>
+      <c r="AO46" s="24"/>
+      <c r="AP46" s="24"/>
+      <c r="AQ46" s="24"/>
+    </row>
+    <row r="55" spans="27:63" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA55" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="20"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
+      <c r="AR55" s="3"/>
+      <c r="AS55" s="20"/>
+      <c r="AT55" s="3"/>
+      <c r="AU55" s="3"/>
+      <c r="AV55" s="3"/>
+      <c r="AW55" s="3"/>
+      <c r="AX55" s="3"/>
+      <c r="AY55" s="3"/>
+      <c r="AZ55" s="3"/>
+      <c r="BA55" s="3"/>
+      <c r="BB55" s="20"/>
+      <c r="BC55" s="3"/>
+      <c r="BD55" s="3"/>
+      <c r="BE55" s="3"/>
+      <c r="BF55" s="3"/>
+      <c r="BG55" s="3"/>
+      <c r="BH55" s="3"/>
+      <c r="BI55" s="3"/>
+      <c r="BJ55" s="3"/>
+      <c r="BK55" s="20"/>
+    </row>
+    <row r="56" spans="27:63" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA56" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="1"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
+      <c r="AR56" s="1"/>
+      <c r="AS56" s="3"/>
+      <c r="AT56" s="3"/>
+      <c r="AU56" s="3"/>
+      <c r="AV56" s="3"/>
+      <c r="AW56" s="3"/>
+      <c r="AX56" s="3"/>
+      <c r="AY56" s="3"/>
+      <c r="AZ56" s="3"/>
+      <c r="BA56" s="1"/>
+      <c r="BB56" s="3"/>
+      <c r="BC56" s="3"/>
+      <c r="BD56" s="3"/>
+      <c r="BE56" s="3"/>
+      <c r="BF56" s="3"/>
+      <c r="BG56" s="3"/>
+      <c r="BH56" s="3"/>
+      <c r="BI56" s="3"/>
+      <c r="BJ56" s="1"/>
+      <c r="BK56" s="3"/>
+    </row>
+    <row r="57" spans="27:63" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA57" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB57" s="3"/>
+      <c r="AC57" s="3"/>
+      <c r="AD57" s="3"/>
+      <c r="AE57" s="3"/>
+      <c r="AF57" s="3"/>
+      <c r="AG57" s="3"/>
+      <c r="AH57" s="1"/>
+      <c r="AI57" s="3"/>
+      <c r="AJ57" s="3"/>
+      <c r="AK57" s="3"/>
+      <c r="AL57" s="3"/>
+      <c r="AM57" s="3"/>
+      <c r="AN57" s="3"/>
+      <c r="AO57" s="3"/>
+      <c r="AP57" s="3"/>
+      <c r="AQ57" s="1"/>
+      <c r="AR57" s="3"/>
+      <c r="AS57" s="3"/>
+      <c r="AT57" s="3"/>
+      <c r="AU57" s="3"/>
+      <c r="AV57" s="3"/>
+      <c r="AW57" s="3"/>
+      <c r="AX57" s="3"/>
+      <c r="AY57" s="3"/>
+      <c r="AZ57" s="1"/>
+      <c r="BA57" s="3"/>
+      <c r="BB57" s="3"/>
+      <c r="BC57" s="3"/>
+      <c r="BD57" s="3"/>
+      <c r="BE57" s="3"/>
+      <c r="BF57" s="3"/>
+      <c r="BG57" s="3"/>
+      <c r="BH57" s="3"/>
+      <c r="BI57" s="1"/>
+      <c r="BJ57" s="3"/>
+      <c r="BK57" s="3"/>
+    </row>
+    <row r="58" spans="27:63" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB58" s="3"/>
+      <c r="AC58" s="3"/>
+      <c r="AD58" s="3"/>
+      <c r="AE58" s="3"/>
+      <c r="AF58" s="3"/>
+      <c r="AG58" s="1"/>
+      <c r="AH58" s="3"/>
+      <c r="AI58" s="3"/>
+      <c r="AJ58" s="3"/>
+      <c r="AK58" s="3"/>
+      <c r="AL58" s="3"/>
+      <c r="AM58" s="3"/>
+      <c r="AN58" s="3"/>
+      <c r="AO58" s="3"/>
+      <c r="AP58" s="1"/>
+      <c r="AQ58" s="3"/>
+      <c r="AR58" s="3"/>
+      <c r="AS58" s="3"/>
+      <c r="AT58" s="3"/>
+      <c r="AU58" s="3"/>
+      <c r="AV58" s="3"/>
+      <c r="AW58" s="3"/>
+      <c r="AX58" s="3"/>
+      <c r="AY58" s="1"/>
+      <c r="AZ58" s="3"/>
+      <c r="BA58" s="3"/>
+      <c r="BB58" s="3"/>
+      <c r="BC58" s="3"/>
+      <c r="BD58" s="3"/>
+      <c r="BE58" s="3"/>
+      <c r="BF58" s="3"/>
+      <c r="BG58" s="3"/>
+      <c r="BH58" s="1"/>
+      <c r="BI58" s="3"/>
+      <c r="BJ58" s="3"/>
+      <c r="BK58" s="3"/>
+    </row>
+    <row r="59" spans="27:63" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3"/>
+      <c r="AC59" s="3"/>
+      <c r="AD59" s="3"/>
+      <c r="AE59" s="3"/>
+      <c r="AF59" s="1"/>
+      <c r="AG59" s="3"/>
+      <c r="AH59" s="3"/>
+      <c r="AI59" s="3"/>
+      <c r="AJ59" s="3"/>
+      <c r="AK59" s="3"/>
+      <c r="AL59" s="3"/>
+      <c r="AM59" s="3"/>
+      <c r="AN59" s="3"/>
+      <c r="AO59" s="1"/>
+      <c r="AP59" s="3"/>
+      <c r="AQ59" s="3"/>
+      <c r="AR59" s="3"/>
+      <c r="AS59" s="3"/>
+      <c r="AT59" s="3"/>
+      <c r="AU59" s="3"/>
+      <c r="AV59" s="3"/>
+      <c r="AW59" s="3"/>
+      <c r="AX59" s="1"/>
+      <c r="AY59" s="3"/>
+      <c r="AZ59" s="3"/>
+      <c r="BA59" s="3"/>
+      <c r="BB59" s="3"/>
+      <c r="BC59" s="3"/>
+      <c r="BD59" s="3"/>
+      <c r="BE59" s="3"/>
+      <c r="BF59" s="3"/>
+      <c r="BG59" s="1"/>
+      <c r="BH59" s="3"/>
+      <c r="BI59" s="3"/>
+      <c r="BJ59" s="3"/>
+      <c r="BK59" s="3"/>
+    </row>
+    <row r="60" spans="27:63" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA60" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB60" s="3"/>
+      <c r="AC60" s="3"/>
+      <c r="AD60" s="3"/>
+      <c r="AE60" s="19"/>
+      <c r="AF60" s="3"/>
+      <c r="AG60" s="3"/>
+      <c r="AH60" s="3"/>
+      <c r="AI60" s="3"/>
+      <c r="AJ60" s="3"/>
+      <c r="AK60" s="3"/>
+      <c r="AL60" s="3"/>
+      <c r="AM60" s="3"/>
+      <c r="AN60" s="19"/>
+      <c r="AO60" s="3"/>
+      <c r="AP60" s="3"/>
+      <c r="AQ60" s="3"/>
+      <c r="AR60" s="3"/>
+      <c r="AS60" s="3"/>
+      <c r="AT60" s="3"/>
+      <c r="AU60" s="3"/>
+      <c r="AV60" s="3"/>
+      <c r="AW60" s="19"/>
+      <c r="AX60" s="3"/>
+      <c r="AY60" s="3"/>
+      <c r="AZ60" s="3"/>
+      <c r="BA60" s="3"/>
+      <c r="BB60" s="3"/>
+      <c r="BC60" s="3"/>
+      <c r="BD60" s="3"/>
+      <c r="BE60" s="3"/>
+      <c r="BF60" s="19"/>
+      <c r="BG60" s="3"/>
+      <c r="BH60" s="3"/>
+      <c r="BI60" s="3"/>
+      <c r="BJ60" s="3"/>
+      <c r="BK60" s="3"/>
+    </row>
+    <row r="61" spans="27:63" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA61" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB61" s="3"/>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="19"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="3"/>
+      <c r="AG61" s="3"/>
+      <c r="AH61" s="3"/>
+      <c r="AI61" s="3"/>
+      <c r="AJ61" s="3"/>
+      <c r="AK61" s="3"/>
+      <c r="AL61" s="3"/>
+      <c r="AM61" s="19"/>
+      <c r="AN61" s="3"/>
+      <c r="AO61" s="3"/>
+      <c r="AP61" s="3"/>
+      <c r="AQ61" s="3"/>
+      <c r="AR61" s="3"/>
+      <c r="AS61" s="3"/>
+      <c r="AT61" s="3"/>
+      <c r="AU61" s="3"/>
+      <c r="AV61" s="19"/>
+      <c r="AW61" s="3"/>
+      <c r="AX61" s="3"/>
+      <c r="AY61" s="3"/>
+      <c r="AZ61" s="3"/>
+      <c r="BA61" s="3"/>
+      <c r="BB61" s="3"/>
+      <c r="BC61" s="3"/>
+      <c r="BD61" s="3"/>
+      <c r="BE61" s="19"/>
+      <c r="BF61" s="3"/>
+      <c r="BG61" s="3"/>
+      <c r="BH61" s="3"/>
+      <c r="BI61" s="3"/>
+      <c r="BJ61" s="3"/>
+      <c r="BK61" s="3"/>
+    </row>
+    <row r="62" spans="27:63" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB62" s="3"/>
+      <c r="AC62" s="19"/>
+      <c r="AD62" s="3"/>
+      <c r="AE62" s="3"/>
+      <c r="AF62" s="3"/>
+      <c r="AG62" s="3"/>
+      <c r="AH62" s="3"/>
+      <c r="AI62" s="3"/>
+      <c r="AJ62" s="3"/>
+      <c r="AK62" s="3"/>
+      <c r="AL62" s="19"/>
+      <c r="AM62" s="3"/>
+      <c r="AN62" s="3"/>
+      <c r="AO62" s="3"/>
+      <c r="AP62" s="3"/>
+      <c r="AQ62" s="3"/>
+      <c r="AR62" s="3"/>
+      <c r="AS62" s="3"/>
+      <c r="AT62" s="3"/>
+      <c r="AU62" s="19"/>
+      <c r="AV62" s="3"/>
+      <c r="AW62" s="3"/>
+      <c r="AX62" s="3"/>
+      <c r="AY62" s="3"/>
+      <c r="AZ62" s="3"/>
+      <c r="BA62" s="3"/>
+      <c r="BB62" s="3"/>
+      <c r="BC62" s="3"/>
+      <c r="BD62" s="19"/>
+      <c r="BE62" s="3"/>
+      <c r="BF62" s="3"/>
+      <c r="BG62" s="3"/>
+      <c r="BH62" s="3"/>
+      <c r="BI62" s="3"/>
+      <c r="BJ62" s="3"/>
+      <c r="BK62" s="3"/>
+    </row>
+    <row r="63" spans="27:63" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA63" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="19"/>
+      <c r="AC63" s="3"/>
+      <c r="AD63" s="3"/>
+      <c r="AE63" s="3"/>
+      <c r="AF63" s="3"/>
+      <c r="AG63" s="3"/>
+      <c r="AH63" s="3"/>
+      <c r="AI63" s="3"/>
+      <c r="AJ63" s="3"/>
+      <c r="AK63" s="19"/>
+      <c r="AL63" s="3"/>
+      <c r="AM63" s="3"/>
+      <c r="AN63" s="3"/>
+      <c r="AO63" s="3"/>
+      <c r="AP63" s="3"/>
+      <c r="AQ63" s="3"/>
+      <c r="AR63" s="3"/>
+      <c r="AS63" s="3"/>
+      <c r="AT63" s="19"/>
+      <c r="AU63" s="3"/>
+      <c r="AV63" s="3"/>
+      <c r="AW63" s="3"/>
+      <c r="AX63" s="3"/>
+      <c r="AY63" s="3"/>
+      <c r="AZ63" s="3"/>
+      <c r="BA63" s="3"/>
+      <c r="BB63" s="3"/>
+      <c r="BC63" s="19"/>
+      <c r="BD63" s="3"/>
+      <c r="BE63" s="3"/>
+      <c r="BF63" s="3"/>
+      <c r="BG63" s="3"/>
+      <c r="BH63" s="3"/>
+      <c r="BI63" s="3"/>
+      <c r="BJ63" s="3"/>
+      <c r="BK63" s="3"/>
+    </row>
+    <row r="65" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB65" s="21"/>
+      <c r="AC65" s="21"/>
+      <c r="AD65" s="21"/>
+      <c r="AE65" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF65" s="1"/>
+      <c r="AG65" s="1"/>
+      <c r="AH65" s="3"/>
+      <c r="AI65" s="3"/>
+      <c r="AJ65" s="20"/>
+      <c r="AK65" s="21"/>
+      <c r="AL65" s="21"/>
+      <c r="AM65" s="21"/>
+      <c r="AN65" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO65" s="1"/>
+      <c r="AP65" s="1"/>
+      <c r="AQ65" s="3"/>
+      <c r="AR65" s="3"/>
+      <c r="AS65" s="20"/>
+      <c r="AT65" s="21"/>
+      <c r="AU65" s="21"/>
+      <c r="AV65" s="21"/>
+      <c r="AW65" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AX65" s="1"/>
+      <c r="AY65" s="1"/>
+      <c r="AZ65" s="3"/>
+      <c r="BA65" s="3"/>
+      <c r="BB65" s="20"/>
+      <c r="BC65" s="21"/>
+      <c r="BD65" s="21"/>
+      <c r="BE65" s="21"/>
+      <c r="BF65" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="BG65" s="1"/>
+      <c r="BH65" s="1"/>
+      <c r="BI65" s="3"/>
+      <c r="BJ65" s="3"/>
+      <c r="BK65" s="20"/>
+      <c r="BM65" s="21"/>
+      <c r="BN65" s="21"/>
+      <c r="BO65" s="21"/>
+      <c r="BP65" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="BQ65" s="1"/>
+      <c r="BR65" s="1"/>
+      <c r="BS65" s="3"/>
+      <c r="BT65" s="3"/>
+      <c r="BU65" s="20"/>
+    </row>
+    <row r="66" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB66" s="3"/>
+      <c r="AC66" s="3"/>
+      <c r="AD66" s="19"/>
+      <c r="AE66" s="19"/>
+      <c r="AF66" s="3"/>
+      <c r="AG66" s="3"/>
+      <c r="AH66" s="3"/>
+      <c r="AI66" s="3"/>
+      <c r="AJ66" s="3"/>
+      <c r="AK66" s="3"/>
+      <c r="AL66" s="3"/>
+      <c r="AM66" s="19"/>
+      <c r="AN66" s="19"/>
+      <c r="AO66" s="3"/>
+      <c r="AP66" s="3"/>
+      <c r="AQ66" s="3"/>
+      <c r="AR66" s="3"/>
+      <c r="AS66" s="3"/>
+      <c r="AT66" s="3"/>
+      <c r="AU66" s="3"/>
+      <c r="AV66" s="19"/>
+      <c r="AW66" s="19"/>
+      <c r="AX66" s="3"/>
+      <c r="AY66" s="3"/>
+      <c r="AZ66" s="3"/>
+      <c r="BA66" s="3"/>
+      <c r="BB66" s="3"/>
+      <c r="BC66" s="3"/>
+      <c r="BD66" s="3"/>
+      <c r="BE66" s="19"/>
+      <c r="BF66" s="19"/>
+      <c r="BG66" s="3"/>
+      <c r="BH66" s="3"/>
+      <c r="BI66" s="3"/>
+      <c r="BJ66" s="3"/>
+      <c r="BK66" s="3"/>
+      <c r="BM66" s="3"/>
+      <c r="BN66" s="3"/>
+      <c r="BO66" s="19"/>
+      <c r="BP66" s="19"/>
+      <c r="BQ66" s="3"/>
+      <c r="BR66" s="3"/>
+      <c r="BS66" s="3"/>
+      <c r="BT66" s="3"/>
+      <c r="BU66" s="3"/>
+    </row>
+    <row r="67" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA67" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB67" s="21"/>
+      <c r="AC67" s="21"/>
+      <c r="AD67" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE67" s="21"/>
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="1"/>
+      <c r="AH67" s="1"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="20"/>
+      <c r="AK67" s="21"/>
+      <c r="AL67" s="21"/>
+      <c r="AM67" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN67" s="21"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="1"/>
+      <c r="AQ67" s="1"/>
+      <c r="AR67" s="3"/>
+      <c r="AS67" s="20"/>
+      <c r="AT67" s="21"/>
+      <c r="AU67" s="21"/>
+      <c r="AV67" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW67" s="21"/>
+      <c r="AX67" s="3"/>
+      <c r="AY67" s="1"/>
+      <c r="AZ67" s="1"/>
+      <c r="BA67" s="3"/>
+      <c r="BB67" s="20"/>
+      <c r="BC67" s="21"/>
+      <c r="BD67" s="21"/>
+      <c r="BE67" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="BF67" s="21"/>
+      <c r="BG67" s="3"/>
+      <c r="BH67" s="1"/>
+      <c r="BI67" s="1"/>
+      <c r="BJ67" s="3"/>
+      <c r="BK67" s="20"/>
+      <c r="BM67" s="21"/>
+      <c r="BN67" s="21"/>
+      <c r="BO67" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="BP67" s="21"/>
+      <c r="BQ67" s="3"/>
+      <c r="BR67" s="1"/>
+      <c r="BS67" s="1"/>
+      <c r="BT67" s="3"/>
+      <c r="BU67" s="20"/>
+    </row>
+    <row r="68" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AA68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB68" s="3"/>
+      <c r="AC68" s="19"/>
+      <c r="AD68" s="19"/>
+      <c r="AE68" s="3"/>
+      <c r="AF68" s="3"/>
+      <c r="AG68" s="3"/>
+      <c r="AH68" s="3"/>
+      <c r="AI68" s="3"/>
+      <c r="AJ68" s="3"/>
+      <c r="AK68" s="3"/>
+      <c r="AL68" s="19"/>
+      <c r="AM68" s="19"/>
+      <c r="AN68" s="3"/>
+      <c r="AO68" s="3"/>
+      <c r="AP68" s="3"/>
+      <c r="AQ68" s="3"/>
+      <c r="AR68" s="3"/>
+      <c r="AS68" s="3"/>
+      <c r="AT68" s="3"/>
+      <c r="AU68" s="19"/>
+      <c r="AV68" s="19"/>
+      <c r="AW68" s="3"/>
+      <c r="AX68" s="3"/>
+      <c r="AY68" s="3"/>
+      <c r="AZ68" s="3"/>
+      <c r="BA68" s="3"/>
+      <c r="BB68" s="3"/>
+      <c r="BC68" s="3"/>
+      <c r="BD68" s="19"/>
+      <c r="BE68" s="19"/>
+      <c r="BF68" s="3"/>
+      <c r="BG68" s="3"/>
+      <c r="BH68" s="3"/>
+      <c r="BI68" s="3"/>
+      <c r="BJ68" s="3"/>
+      <c r="BK68" s="3"/>
+      <c r="BM68" s="3"/>
+      <c r="BN68" s="19"/>
+      <c r="BO68" s="19"/>
+      <c r="BP68" s="3"/>
+      <c r="BQ68" s="3"/>
+      <c r="BR68" s="3"/>
+      <c r="BS68" s="3"/>
+      <c r="BT68" s="3"/>
+      <c r="BU68" s="3"/>
+    </row>
+    <row r="69" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N69" s="2">
+        <v>4</v>
+      </c>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="19"/>
+      <c r="R69" s="19"/>
+      <c r="T69" s="2">
+        <v>4</v>
+      </c>
+      <c r="U69" s="1"/>
+      <c r="V69" s="1"/>
+      <c r="W69" s="3"/>
+      <c r="X69" s="3"/>
+      <c r="AA69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB69" s="21"/>
+      <c r="AC69" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD69" s="21"/>
+      <c r="AE69" s="21"/>
+      <c r="AF69" s="3"/>
+      <c r="AG69" s="3"/>
+      <c r="AH69" s="1"/>
+      <c r="AI69" s="1"/>
+      <c r="AJ69" s="20"/>
+      <c r="AK69" s="21"/>
+      <c r="AL69" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM69" s="21"/>
+      <c r="AN69" s="21"/>
+      <c r="AO69" s="3"/>
+      <c r="AP69" s="3"/>
+      <c r="AQ69" s="1"/>
+      <c r="AR69" s="1"/>
+      <c r="AS69" s="20"/>
+      <c r="AT69" s="21"/>
+      <c r="AU69" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV69" s="21"/>
+      <c r="AW69" s="21"/>
+      <c r="AX69" s="3"/>
+      <c r="AY69" s="3"/>
+      <c r="AZ69" s="1"/>
+      <c r="BA69" s="1"/>
+      <c r="BB69" s="20"/>
+      <c r="BC69" s="21"/>
+      <c r="BD69" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE69" s="21"/>
+      <c r="BF69" s="21"/>
+      <c r="BG69" s="3"/>
+      <c r="BH69" s="3"/>
+      <c r="BI69" s="1"/>
+      <c r="BJ69" s="1"/>
+      <c r="BK69" s="20"/>
+      <c r="BM69" s="21"/>
+      <c r="BN69" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="BO69" s="21"/>
+      <c r="BP69" s="21"/>
+      <c r="BQ69" s="3"/>
+      <c r="BR69" s="3"/>
+      <c r="BS69" s="1"/>
+      <c r="BT69" s="1"/>
+      <c r="BU69" s="20"/>
+    </row>
+    <row r="70" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N70" s="2">
+        <v>3</v>
+      </c>
+      <c r="O70" s="3"/>
+      <c r="P70" s="19"/>
+      <c r="Q70" s="19"/>
+      <c r="R70" s="3"/>
+      <c r="T70" s="2">
+        <v>3</v>
+      </c>
+      <c r="U70" s="3"/>
+      <c r="V70" s="1"/>
+      <c r="W70" s="1"/>
+      <c r="X70" s="3"/>
+      <c r="AA70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB70" s="19"/>
+      <c r="AC70" s="19"/>
+      <c r="AD70" s="3"/>
+      <c r="AE70" s="3"/>
+      <c r="AF70" s="3"/>
+      <c r="AG70" s="3"/>
+      <c r="AH70" s="3"/>
+      <c r="AI70" s="3"/>
+      <c r="AJ70" s="3"/>
+      <c r="AK70" s="19"/>
+      <c r="AL70" s="19"/>
+      <c r="AM70" s="3"/>
+      <c r="AN70" s="3"/>
+      <c r="AO70" s="3"/>
+      <c r="AP70" s="3"/>
+      <c r="AQ70" s="3"/>
+      <c r="AR70" s="3"/>
+      <c r="AS70" s="3"/>
+      <c r="AT70" s="19"/>
+      <c r="AU70" s="19"/>
+      <c r="AV70" s="3"/>
+      <c r="AW70" s="3"/>
+      <c r="AX70" s="3"/>
+      <c r="AY70" s="3"/>
+      <c r="AZ70" s="3"/>
+      <c r="BA70" s="3"/>
+      <c r="BB70" s="3"/>
+      <c r="BC70" s="19"/>
+      <c r="BD70" s="19"/>
+      <c r="BE70" s="3"/>
+      <c r="BF70" s="3"/>
+      <c r="BG70" s="3"/>
+      <c r="BH70" s="3"/>
+      <c r="BI70" s="3"/>
+      <c r="BJ70" s="3"/>
+      <c r="BK70" s="3"/>
+      <c r="BM70" s="19"/>
+      <c r="BN70" s="19"/>
+      <c r="BO70" s="3"/>
+      <c r="BP70" s="3"/>
+      <c r="BQ70" s="3"/>
+      <c r="BR70" s="3"/>
+      <c r="BS70" s="3"/>
+      <c r="BT70" s="3"/>
+      <c r="BU70" s="3"/>
+    </row>
+    <row r="71" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N71" s="2">
+        <v>2</v>
+      </c>
+      <c r="O71" s="19"/>
+      <c r="P71" s="19"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="3"/>
+      <c r="T71" s="2">
+        <v>2</v>
+      </c>
+      <c r="U71" s="3"/>
+      <c r="V71" s="3"/>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="AA71" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB71" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC71" s="21"/>
+      <c r="AD71" s="21"/>
+      <c r="AE71" s="21"/>
+      <c r="AF71" s="1"/>
+      <c r="AG71" s="3"/>
+      <c r="AH71" s="3"/>
+      <c r="AI71" s="1"/>
+      <c r="AJ71" s="20"/>
+      <c r="AK71" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL71" s="21"/>
+      <c r="AM71" s="21"/>
+      <c r="AN71" s="21"/>
+      <c r="AO71" s="1"/>
+      <c r="AP71" s="3"/>
+      <c r="AQ71" s="3"/>
+      <c r="AR71" s="1"/>
+      <c r="AS71" s="20"/>
+      <c r="AT71" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU71" s="21"/>
+      <c r="AV71" s="21"/>
+      <c r="AW71" s="21"/>
+      <c r="AX71" s="1"/>
+      <c r="AY71" s="3"/>
+      <c r="AZ71" s="3"/>
+      <c r="BA71" s="1"/>
+      <c r="BB71" s="20"/>
+      <c r="BC71" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="BD71" s="21"/>
+      <c r="BE71" s="21"/>
+      <c r="BF71" s="21"/>
+      <c r="BG71" s="1"/>
+      <c r="BH71" s="3"/>
+      <c r="BI71" s="3"/>
+      <c r="BJ71" s="1"/>
+      <c r="BK71" s="20"/>
+      <c r="BM71" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN71" s="21"/>
+      <c r="BO71" s="21"/>
+      <c r="BP71" s="21"/>
+      <c r="BQ71" s="1"/>
+      <c r="BR71" s="3"/>
+      <c r="BS71" s="3"/>
+      <c r="BT71" s="1"/>
+      <c r="BU71" s="20"/>
+    </row>
+    <row r="72" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N72" s="2">
+        <v>1</v>
+      </c>
+      <c r="O72" s="19"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="19"/>
+      <c r="T72" s="2">
+        <v>1</v>
+      </c>
+      <c r="U72" s="1"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="1"/>
+      <c r="AA72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB72" s="19"/>
+      <c r="AC72" s="3"/>
+      <c r="AD72" s="3"/>
+      <c r="AE72" s="19"/>
+      <c r="AF72" s="3"/>
+      <c r="AG72" s="3"/>
+      <c r="AH72" s="3"/>
+      <c r="AI72" s="3"/>
+      <c r="AJ72" s="3"/>
+      <c r="AK72" s="19"/>
+      <c r="AL72" s="3"/>
+      <c r="AM72" s="3"/>
+      <c r="AN72" s="19"/>
+      <c r="AO72" s="3"/>
+      <c r="AP72" s="3"/>
+      <c r="AQ72" s="3"/>
+      <c r="AR72" s="3"/>
+      <c r="AS72" s="3"/>
+      <c r="AT72" s="19"/>
+      <c r="AU72" s="3"/>
+      <c r="AV72" s="3"/>
+      <c r="AW72" s="19"/>
+      <c r="AX72" s="3"/>
+      <c r="AY72" s="3"/>
+      <c r="AZ72" s="3"/>
+      <c r="BA72" s="3"/>
+      <c r="BB72" s="3"/>
+      <c r="BC72" s="19"/>
+      <c r="BD72" s="3"/>
+      <c r="BE72" s="3"/>
+      <c r="BF72" s="19"/>
+      <c r="BG72" s="3"/>
+      <c r="BH72" s="3"/>
+      <c r="BI72" s="3"/>
+      <c r="BJ72" s="3"/>
+      <c r="BK72" s="3"/>
+      <c r="BM72" s="19"/>
+      <c r="BN72" s="3"/>
+      <c r="BO72" s="3"/>
+      <c r="BP72" s="19"/>
+      <c r="BQ72" s="3"/>
+      <c r="BR72" s="3"/>
+      <c r="BS72" s="3"/>
+      <c r="BT72" s="3"/>
+      <c r="BU72" s="3"/>
+    </row>
+    <row r="73" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N73" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O73" s="2">
+        <v>1</v>
+      </c>
+      <c r="P73" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>3</v>
+      </c>
+      <c r="R73" s="2">
+        <v>4</v>
+      </c>
+      <c r="T73" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="U73" s="2">
+        <v>1</v>
+      </c>
+      <c r="V73" s="2">
+        <v>2</v>
+      </c>
+      <c r="W73" s="2">
+        <v>3</v>
+      </c>
+      <c r="X73" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA73" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ73" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS73" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AT73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AX73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AZ73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BA73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BB73" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BC73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BD73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BE73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BG73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BH73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BI73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BK73" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM73" s="2">
+        <v>1</v>
+      </c>
+      <c r="BN73" s="2">
+        <v>2</v>
+      </c>
+      <c r="BO73" s="2">
+        <v>3</v>
+      </c>
+      <c r="BP73" s="2">
+        <v>4</v>
+      </c>
+      <c r="BQ73" s="2">
+        <v>5</v>
+      </c>
+      <c r="BR73" s="2">
+        <v>6</v>
+      </c>
+      <c r="BS73" s="2">
+        <v>7</v>
+      </c>
+      <c r="BT73" s="2">
+        <v>8</v>
+      </c>
+      <c r="BU73" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF76" s="19"/>
+      <c r="AH76" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI76" s="24"/>
+      <c r="AJ76" s="24"/>
+      <c r="AK76" s="24"/>
+      <c r="AL76" s="24"/>
+      <c r="AM76" s="24"/>
+      <c r="AN76" s="24"/>
+      <c r="AO76" s="24"/>
+      <c r="AP76" s="24"/>
+      <c r="AQ76" s="24"/>
+      <c r="AR76" s="24"/>
+      <c r="AS76" s="24"/>
+      <c r="AT76" s="24"/>
+      <c r="AU76" s="24"/>
+    </row>
+    <row r="78" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF78" s="1"/>
+      <c r="AH78" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI78" s="24"/>
+      <c r="AJ78" s="24"/>
+      <c r="AK78" s="24"/>
+      <c r="AL78" s="24"/>
+      <c r="AM78" s="24"/>
+      <c r="AN78" s="24"/>
+      <c r="AO78" s="24"/>
+      <c r="AP78" s="24"/>
+      <c r="AQ78" s="24"/>
+      <c r="AR78" s="24"/>
+      <c r="AS78" s="24"/>
+      <c r="AT78" s="24"/>
+      <c r="AU78" s="24"/>
+    </row>
+    <row r="80" spans="14:73" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF80" s="20"/>
+      <c r="AH80" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI80" s="24"/>
+      <c r="AJ80" s="24"/>
+      <c r="AK80" s="24"/>
+      <c r="AL80" s="24"/>
+      <c r="AM80" s="24"/>
+      <c r="AN80" s="24"/>
+      <c r="AO80" s="24"/>
+      <c r="AP80" s="24"/>
+      <c r="AQ80" s="24"/>
+      <c r="AR80" s="24"/>
+      <c r="AS80" s="24"/>
+      <c r="AT80" s="24"/>
+      <c r="AU80" s="24"/>
+    </row>
+    <row r="82" spans="32:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF82" s="21"/>
+      <c r="AH82" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI82" s="24"/>
+      <c r="AJ82" s="24"/>
+      <c r="AK82" s="24"/>
+      <c r="AL82" s="24"/>
+      <c r="AM82" s="24"/>
+      <c r="AN82" s="24"/>
+      <c r="AO82" s="24"/>
+      <c r="AP82" s="24"/>
+      <c r="AQ82" s="24"/>
+      <c r="AR82" s="24"/>
+      <c r="AS82" s="24"/>
+      <c r="AT82" s="24"/>
+      <c r="AU82" s="24"/>
+    </row>
+    <row r="84" spans="32:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF84" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH84" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI84" s="24"/>
+      <c r="AJ84" s="24"/>
+      <c r="AK84" s="24"/>
+      <c r="AL84" s="24"/>
+      <c r="AM84" s="24"/>
+      <c r="AN84" s="24"/>
+      <c r="AO84" s="24"/>
+      <c r="AP84" s="24"/>
+      <c r="AQ84" s="24"/>
+      <c r="AR84" s="24"/>
+      <c r="AS84" s="24"/>
+      <c r="AT84" s="24"/>
+      <c r="AU84" s="24"/>
+    </row>
+    <row r="86" spans="32:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF86" s="3"/>
+      <c r="AH86" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI86" s="24"/>
+      <c r="AJ86" s="24"/>
+      <c r="AK86" s="24"/>
+      <c r="AL86" s="24"/>
+      <c r="AM86" s="24"/>
+      <c r="AN86" s="24"/>
+      <c r="AO86" s="24"/>
+      <c r="AP86" s="24"/>
+      <c r="AQ86" s="24"/>
+      <c r="AR86" s="24"/>
+      <c r="AS86" s="24"/>
+      <c r="AT86" s="24"/>
+      <c r="AU86" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="13">
     <mergeCell ref="AD46:AQ46"/>
     <mergeCell ref="I36:L36"/>
     <mergeCell ref="S36:V36"/>
@@ -4818,6 +5991,12 @@
     <mergeCell ref="AD40:AQ40"/>
     <mergeCell ref="AD42:AQ42"/>
     <mergeCell ref="AD44:AQ44"/>
+    <mergeCell ref="AH86:AU86"/>
+    <mergeCell ref="AH76:AU76"/>
+    <mergeCell ref="AH78:AU78"/>
+    <mergeCell ref="AH80:AU80"/>
+    <mergeCell ref="AH82:AU82"/>
+    <mergeCell ref="AH84:AU84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4826,7 +6005,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650278B7-1223-4149-BA89-05809BD68F8E}">
-  <dimension ref="F2:EC62"/>
+  <dimension ref="F2:EC63"/>
   <sheetFormatPr defaultColWidth="3.5546875" defaultRowHeight="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="26" width="3.5546875" style="2"/>
@@ -7701,808 +8880,891 @@
       </c>
     </row>
     <row r="37" spans="6:133" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I37" s="23" t="s">
+      <c r="I37" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="J37" s="23"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23"/>
-      <c r="S37" s="23" t="s">
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="S37" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="T37" s="23"/>
-      <c r="U37" s="23"/>
-      <c r="V37" s="23"/>
+      <c r="T37" s="24"/>
+      <c r="U37" s="24"/>
+      <c r="V37" s="24"/>
     </row>
     <row r="39" spans="6:133" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB39" s="4"/>
-      <c r="AD39" s="23" t="s">
+      <c r="AD39" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="AE39" s="23"/>
-      <c r="AF39" s="23"/>
-      <c r="AG39" s="23"/>
-      <c r="AH39" s="23"/>
-      <c r="AI39" s="23"/>
-      <c r="AJ39" s="23"/>
-      <c r="AK39" s="23"/>
-      <c r="AL39" s="23"/>
-      <c r="AM39" s="23"/>
-      <c r="AN39" s="23"/>
-      <c r="AO39" s="23"/>
-      <c r="AP39" s="23"/>
-      <c r="AQ39" s="23"/>
+      <c r="AE39" s="24"/>
+      <c r="AF39" s="24"/>
+      <c r="AG39" s="24"/>
+      <c r="AH39" s="24"/>
+      <c r="AI39" s="24"/>
+      <c r="AJ39" s="24"/>
+      <c r="AK39" s="24"/>
+      <c r="AL39" s="24"/>
+      <c r="AM39" s="24"/>
+      <c r="AN39" s="24"/>
+      <c r="AO39" s="24"/>
+      <c r="AP39" s="24"/>
+      <c r="AQ39" s="24"/>
     </row>
     <row r="41" spans="6:133" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB41" s="5"/>
-      <c r="AD41" s="23" t="s">
+      <c r="AD41" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="AE41" s="23"/>
-      <c r="AF41" s="23"/>
-      <c r="AG41" s="23"/>
-      <c r="AH41" s="23"/>
-      <c r="AI41" s="23"/>
-      <c r="AJ41" s="23"/>
-      <c r="AK41" s="23"/>
-      <c r="AL41" s="23"/>
-      <c r="AM41" s="23"/>
-      <c r="AN41" s="23"/>
-      <c r="AO41" s="23"/>
-      <c r="AP41" s="23"/>
-      <c r="AQ41" s="23"/>
-      <c r="CB41" s="2">
-        <v>4</v>
-      </c>
-      <c r="CC41" s="3"/>
-      <c r="CD41" s="3"/>
-      <c r="CE41" s="21"/>
-      <c r="CF41" s="21"/>
-      <c r="CH41" s="2">
-        <v>4</v>
-      </c>
-      <c r="CI41" s="1"/>
-      <c r="CJ41" s="1"/>
-      <c r="CK41" s="3"/>
-      <c r="CL41" s="3"/>
-      <c r="CQ41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="CR41" s="22"/>
-      <c r="CS41" s="22"/>
-      <c r="CT41" s="22"/>
-      <c r="CU41" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="CV41" s="1"/>
-      <c r="CW41" s="1"/>
-      <c r="CX41" s="3"/>
-      <c r="CY41" s="3"/>
-      <c r="CZ41" s="20"/>
-      <c r="DA41" s="22"/>
-      <c r="DB41" s="22"/>
-      <c r="DC41" s="22"/>
-      <c r="DD41" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DE41" s="1"/>
-      <c r="DF41" s="1"/>
-      <c r="DG41" s="3"/>
-      <c r="DH41" s="3"/>
-      <c r="DI41" s="20"/>
-      <c r="DJ41" s="22"/>
-      <c r="DK41" s="22"/>
-      <c r="DL41" s="22"/>
-      <c r="DM41" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DN41" s="1"/>
-      <c r="DO41" s="1"/>
-      <c r="DP41" s="3"/>
-      <c r="DQ41" s="3"/>
-      <c r="DR41" s="20"/>
-      <c r="DS41" s="22"/>
-      <c r="DT41" s="22"/>
-      <c r="DU41" s="22"/>
-      <c r="DV41" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DW41" s="1"/>
-      <c r="DX41" s="1"/>
-      <c r="DY41" s="3"/>
-      <c r="DZ41" s="3"/>
-      <c r="EA41" s="20"/>
-    </row>
-    <row r="42" spans="6:133" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CB42" s="2">
-        <v>3</v>
-      </c>
-      <c r="CC42" s="3"/>
-      <c r="CD42" s="21"/>
-      <c r="CE42" s="21"/>
-      <c r="CF42" s="3"/>
-      <c r="CH42" s="2">
-        <v>3</v>
-      </c>
-      <c r="CI42" s="3"/>
-      <c r="CJ42" s="1"/>
-      <c r="CK42" s="1"/>
-      <c r="CL42" s="3"/>
-      <c r="CQ42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="CR42" s="3"/>
-      <c r="CS42" s="3"/>
-      <c r="CT42" s="21"/>
-      <c r="CU42" s="21"/>
-      <c r="CV42" s="3"/>
-      <c r="CW42" s="3"/>
-      <c r="CX42" s="3"/>
-      <c r="CY42" s="3"/>
-      <c r="CZ42" s="3"/>
-      <c r="DA42" s="3"/>
-      <c r="DB42" s="3"/>
-      <c r="DC42" s="21"/>
-      <c r="DD42" s="21"/>
-      <c r="DE42" s="3"/>
-      <c r="DF42" s="3"/>
-      <c r="DG42" s="3"/>
-      <c r="DH42" s="3"/>
-      <c r="DI42" s="3"/>
-      <c r="DJ42" s="3"/>
-      <c r="DK42" s="3"/>
-      <c r="DL42" s="21"/>
-      <c r="DM42" s="21"/>
-      <c r="DN42" s="3"/>
-      <c r="DO42" s="3"/>
-      <c r="DP42" s="3"/>
-      <c r="DQ42" s="3"/>
-      <c r="DR42" s="3"/>
-      <c r="DS42" s="3"/>
-      <c r="DT42" s="3"/>
-      <c r="DU42" s="21"/>
-      <c r="DV42" s="21"/>
-      <c r="DW42" s="3"/>
-      <c r="DX42" s="3"/>
-      <c r="DY42" s="3"/>
-      <c r="DZ42" s="3"/>
-      <c r="EA42" s="3"/>
+      <c r="AE41" s="24"/>
+      <c r="AF41" s="24"/>
+      <c r="AG41" s="24"/>
+      <c r="AH41" s="24"/>
+      <c r="AI41" s="24"/>
+      <c r="AJ41" s="24"/>
+      <c r="AK41" s="24"/>
+      <c r="AL41" s="24"/>
+      <c r="AM41" s="24"/>
+      <c r="AN41" s="24"/>
+      <c r="AO41" s="24"/>
+      <c r="AP41" s="24"/>
+      <c r="AQ41" s="24"/>
     </row>
     <row r="43" spans="6:133" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB43" s="1"/>
-      <c r="AD43" s="23" t="s">
+      <c r="AD43" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="AE43" s="23"/>
-      <c r="AF43" s="23"/>
-      <c r="AG43" s="23"/>
-      <c r="AH43" s="23"/>
-      <c r="AI43" s="23"/>
-      <c r="AJ43" s="23"/>
-      <c r="AK43" s="23"/>
-      <c r="AL43" s="23"/>
-      <c r="AM43" s="23"/>
-      <c r="AN43" s="23"/>
-      <c r="AO43" s="23"/>
-      <c r="AP43" s="23"/>
-      <c r="AQ43" s="23"/>
-      <c r="CB43" s="2">
-        <v>2</v>
-      </c>
-      <c r="CC43" s="21"/>
-      <c r="CD43" s="21"/>
-      <c r="CE43" s="3"/>
-      <c r="CF43" s="3"/>
-      <c r="CH43" s="2">
-        <v>2</v>
-      </c>
-      <c r="CI43" s="3"/>
-      <c r="CJ43" s="3"/>
-      <c r="CK43" s="1"/>
-      <c r="CL43" s="1"/>
-      <c r="CQ43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="CR43" s="22"/>
-      <c r="CS43" s="22"/>
-      <c r="CT43" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="CU43" s="22"/>
-      <c r="CV43" s="3"/>
-      <c r="CW43" s="1"/>
-      <c r="CX43" s="1"/>
-      <c r="CY43" s="3"/>
-      <c r="CZ43" s="20"/>
-      <c r="DA43" s="22"/>
-      <c r="DB43" s="22"/>
-      <c r="DC43" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DD43" s="22"/>
-      <c r="DE43" s="3"/>
-      <c r="DF43" s="1"/>
-      <c r="DG43" s="1"/>
-      <c r="DH43" s="3"/>
-      <c r="DI43" s="20"/>
-      <c r="DJ43" s="22"/>
-      <c r="DK43" s="22"/>
-      <c r="DL43" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DM43" s="22"/>
-      <c r="DN43" s="3"/>
-      <c r="DO43" s="1"/>
-      <c r="DP43" s="1"/>
-      <c r="DQ43" s="3"/>
-      <c r="DR43" s="20"/>
-      <c r="DS43" s="22"/>
-      <c r="DT43" s="22"/>
-      <c r="DU43" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DV43" s="22"/>
-      <c r="DW43" s="3"/>
-      <c r="DX43" s="1"/>
-      <c r="DY43" s="1"/>
-      <c r="DZ43" s="3"/>
-      <c r="EA43" s="20"/>
-    </row>
-    <row r="44" spans="6:133" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CB44" s="2">
-        <v>1</v>
-      </c>
-      <c r="CC44" s="21"/>
-      <c r="CD44" s="3"/>
-      <c r="CE44" s="3"/>
-      <c r="CF44" s="21"/>
-      <c r="CH44" s="2">
-        <v>1</v>
-      </c>
-      <c r="CI44" s="1"/>
-      <c r="CJ44" s="3"/>
-      <c r="CK44" s="3"/>
-      <c r="CL44" s="1"/>
-      <c r="CQ44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="CR44" s="3"/>
-      <c r="CS44" s="21"/>
-      <c r="CT44" s="21"/>
-      <c r="CU44" s="3"/>
-      <c r="CV44" s="3"/>
-      <c r="CW44" s="3"/>
-      <c r="CX44" s="3"/>
-      <c r="CY44" s="3"/>
-      <c r="CZ44" s="3"/>
-      <c r="DA44" s="3"/>
-      <c r="DB44" s="21"/>
-      <c r="DC44" s="21"/>
-      <c r="DD44" s="3"/>
-      <c r="DE44" s="3"/>
-      <c r="DF44" s="3"/>
-      <c r="DG44" s="3"/>
-      <c r="DH44" s="3"/>
-      <c r="DI44" s="3"/>
-      <c r="DJ44" s="3"/>
-      <c r="DK44" s="21"/>
-      <c r="DL44" s="21"/>
-      <c r="DM44" s="3"/>
-      <c r="DN44" s="3"/>
-      <c r="DO44" s="3"/>
-      <c r="DP44" s="3"/>
-      <c r="DQ44" s="3"/>
-      <c r="DR44" s="3"/>
-      <c r="DS44" s="3"/>
-      <c r="DT44" s="21"/>
-      <c r="DU44" s="21"/>
-      <c r="DV44" s="3"/>
-      <c r="DW44" s="3"/>
-      <c r="DX44" s="3"/>
-      <c r="DY44" s="3"/>
-      <c r="DZ44" s="3"/>
-      <c r="EA44" s="3"/>
+      <c r="AE43" s="24"/>
+      <c r="AF43" s="24"/>
+      <c r="AG43" s="24"/>
+      <c r="AH43" s="24"/>
+      <c r="AI43" s="24"/>
+      <c r="AJ43" s="24"/>
+      <c r="AK43" s="24"/>
+      <c r="AL43" s="24"/>
+      <c r="AM43" s="24"/>
+      <c r="AN43" s="24"/>
+      <c r="AO43" s="24"/>
+      <c r="AP43" s="24"/>
+      <c r="AQ43" s="24"/>
     </row>
     <row r="45" spans="6:133" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB45" s="11"/>
-      <c r="AD45" s="23" t="s">
+      <c r="AD45" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AE45" s="23"/>
-      <c r="AF45" s="23"/>
-      <c r="AG45" s="23"/>
-      <c r="AH45" s="23"/>
-      <c r="AI45" s="23"/>
-      <c r="AJ45" s="23"/>
-      <c r="AK45" s="23"/>
-      <c r="AL45" s="23"/>
-      <c r="AM45" s="23"/>
-      <c r="AN45" s="23"/>
-      <c r="AO45" s="23"/>
-      <c r="AP45" s="23"/>
-      <c r="AQ45" s="23"/>
-      <c r="CB45" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="CC45" s="2">
-        <v>1</v>
-      </c>
-      <c r="CD45" s="2">
-        <v>2</v>
-      </c>
-      <c r="CE45" s="2">
-        <v>3</v>
-      </c>
-      <c r="CF45" s="2">
-        <v>4</v>
-      </c>
-      <c r="CH45" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="CI45" s="2">
-        <v>1</v>
-      </c>
-      <c r="CJ45" s="2">
-        <v>2</v>
-      </c>
-      <c r="CK45" s="2">
-        <v>3</v>
-      </c>
-      <c r="CL45" s="2">
-        <v>4</v>
-      </c>
-      <c r="CQ45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="CR45" s="22"/>
-      <c r="CS45" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="CT45" s="22"/>
-      <c r="CU45" s="22"/>
-      <c r="CV45" s="3"/>
-      <c r="CW45" s="3"/>
-      <c r="CX45" s="1"/>
-      <c r="CY45" s="1"/>
-      <c r="CZ45" s="20"/>
-      <c r="DA45" s="22"/>
-      <c r="DB45" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DC45" s="22"/>
-      <c r="DD45" s="22"/>
-      <c r="DE45" s="3"/>
-      <c r="DF45" s="3"/>
-      <c r="DG45" s="1"/>
-      <c r="DH45" s="1"/>
-      <c r="DI45" s="20"/>
-      <c r="DJ45" s="22"/>
-      <c r="DK45" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DL45" s="22"/>
-      <c r="DM45" s="22"/>
-      <c r="DN45" s="3"/>
-      <c r="DO45" s="3"/>
-      <c r="DP45" s="1"/>
-      <c r="DQ45" s="1"/>
-      <c r="DR45" s="20"/>
-      <c r="DS45" s="22"/>
-      <c r="DT45" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DU45" s="22"/>
-      <c r="DV45" s="22"/>
-      <c r="DW45" s="3"/>
-      <c r="DX45" s="3"/>
-      <c r="DY45" s="1"/>
-      <c r="DZ45" s="1"/>
-      <c r="EA45" s="20"/>
-    </row>
-    <row r="46" spans="6:133" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CQ46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="CR46" s="21"/>
-      <c r="CS46" s="21"/>
-      <c r="CT46" s="3"/>
-      <c r="CU46" s="3"/>
-      <c r="CV46" s="3"/>
-      <c r="CW46" s="3"/>
-      <c r="CX46" s="3"/>
-      <c r="CY46" s="3"/>
-      <c r="CZ46" s="3"/>
-      <c r="DA46" s="21"/>
-      <c r="DB46" s="21"/>
-      <c r="DC46" s="3"/>
-      <c r="DD46" s="3"/>
-      <c r="DE46" s="3"/>
-      <c r="DF46" s="3"/>
-      <c r="DG46" s="3"/>
-      <c r="DH46" s="3"/>
-      <c r="DI46" s="3"/>
-      <c r="DJ46" s="21"/>
-      <c r="DK46" s="21"/>
-      <c r="DL46" s="3"/>
-      <c r="DM46" s="3"/>
-      <c r="DN46" s="3"/>
-      <c r="DO46" s="3"/>
-      <c r="DP46" s="3"/>
-      <c r="DQ46" s="3"/>
-      <c r="DR46" s="3"/>
-      <c r="DS46" s="21"/>
-      <c r="DT46" s="21"/>
-      <c r="DU46" s="3"/>
-      <c r="DV46" s="3"/>
-      <c r="DW46" s="3"/>
-      <c r="DX46" s="3"/>
-      <c r="DY46" s="3"/>
-      <c r="DZ46" s="3"/>
-      <c r="EA46" s="3"/>
+      <c r="AE45" s="24"/>
+      <c r="AF45" s="24"/>
+      <c r="AG45" s="24"/>
+      <c r="AH45" s="24"/>
+      <c r="AI45" s="24"/>
+      <c r="AJ45" s="24"/>
+      <c r="AK45" s="24"/>
+      <c r="AL45" s="24"/>
+      <c r="AM45" s="24"/>
+      <c r="AN45" s="24"/>
+      <c r="AO45" s="24"/>
+      <c r="AP45" s="24"/>
+      <c r="AQ45" s="24"/>
     </row>
     <row r="47" spans="6:133" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB47" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AD47" s="23" t="s">
+      <c r="AD47" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="AE47" s="23"/>
-      <c r="AF47" s="23"/>
-      <c r="AG47" s="23"/>
-      <c r="AH47" s="23"/>
-      <c r="AI47" s="23"/>
-      <c r="AJ47" s="23"/>
-      <c r="AK47" s="23"/>
-      <c r="AL47" s="23"/>
-      <c r="AM47" s="23"/>
-      <c r="AN47" s="23"/>
-      <c r="AO47" s="23"/>
-      <c r="AP47" s="23"/>
-      <c r="AQ47" s="23"/>
-      <c r="CQ47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="CR47" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="CS47" s="22"/>
-      <c r="CT47" s="22"/>
-      <c r="CU47" s="22"/>
-      <c r="CV47" s="3"/>
-      <c r="CW47" s="3"/>
-      <c r="CX47" s="3"/>
-      <c r="CY47" s="1"/>
-      <c r="CZ47" s="20"/>
-      <c r="DA47" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DB47" s="22"/>
-      <c r="DC47" s="22"/>
-      <c r="DD47" s="22"/>
-      <c r="DE47" s="3"/>
-      <c r="DF47" s="3"/>
-      <c r="DG47" s="3"/>
-      <c r="DH47" s="1"/>
-      <c r="DI47" s="20"/>
-      <c r="DJ47" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DK47" s="22"/>
-      <c r="DL47" s="22"/>
-      <c r="DM47" s="22"/>
-      <c r="DN47" s="3"/>
-      <c r="DO47" s="3"/>
-      <c r="DP47" s="3"/>
-      <c r="DQ47" s="1"/>
-      <c r="DR47" s="20"/>
-      <c r="DS47" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="DT47" s="22"/>
-      <c r="DU47" s="22"/>
-      <c r="DV47" s="22"/>
-      <c r="DW47" s="3"/>
-      <c r="DX47" s="3"/>
-      <c r="DY47" s="3"/>
-      <c r="DZ47" s="1"/>
-      <c r="EA47" s="20"/>
+      <c r="AE47" s="24"/>
+      <c r="AF47" s="24"/>
+      <c r="AG47" s="24"/>
+      <c r="AH47" s="24"/>
+      <c r="AI47" s="24"/>
+      <c r="AJ47" s="24"/>
+      <c r="AK47" s="24"/>
+      <c r="AL47" s="24"/>
+      <c r="AM47" s="24"/>
+      <c r="AN47" s="24"/>
+      <c r="AO47" s="24"/>
+      <c r="AP47" s="24"/>
+      <c r="AQ47" s="24"/>
+      <c r="AX47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY47" s="20"/>
+      <c r="AZ47" s="20"/>
+      <c r="BA47" s="1"/>
+      <c r="BB47" s="10"/>
+      <c r="BC47" s="20"/>
+      <c r="BD47" s="20"/>
+      <c r="BE47" s="1"/>
+      <c r="BF47" s="10"/>
+      <c r="BG47" s="20"/>
+      <c r="BH47" s="20"/>
+      <c r="BI47" s="1"/>
+      <c r="BJ47" s="10"/>
+      <c r="BK47" s="20"/>
+      <c r="BL47" s="20"/>
+      <c r="BM47" s="1"/>
+      <c r="BN47" s="10"/>
+      <c r="BO47" s="20"/>
+      <c r="BP47" s="20"/>
+      <c r="BQ47" s="3"/>
+      <c r="BR47" s="10"/>
+      <c r="BS47" s="20"/>
+      <c r="BT47" s="20"/>
+      <c r="BU47" s="26"/>
+      <c r="BV47" s="10"/>
+      <c r="BW47" s="20"/>
+      <c r="BX47" s="20"/>
+      <c r="BY47" s="26"/>
+      <c r="BZ47" s="10"/>
     </row>
     <row r="48" spans="6:133" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CQ48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="CR48" s="21"/>
-      <c r="CS48" s="3"/>
-      <c r="CT48" s="3"/>
-      <c r="CU48" s="21"/>
-      <c r="CV48" s="1"/>
-      <c r="CW48" s="3"/>
-      <c r="CX48" s="3"/>
-      <c r="CY48" s="3"/>
-      <c r="CZ48" s="3"/>
-      <c r="DA48" s="21"/>
-      <c r="DB48" s="3"/>
-      <c r="DC48" s="3"/>
-      <c r="DD48" s="21"/>
-      <c r="DE48" s="1"/>
-      <c r="DF48" s="3"/>
-      <c r="DG48" s="3"/>
-      <c r="DH48" s="3"/>
-      <c r="DI48" s="3"/>
-      <c r="DJ48" s="21"/>
-      <c r="DK48" s="3"/>
-      <c r="DL48" s="3"/>
-      <c r="DM48" s="21"/>
-      <c r="DN48" s="1"/>
-      <c r="DO48" s="3"/>
-      <c r="DP48" s="3"/>
-      <c r="DQ48" s="3"/>
-      <c r="DR48" s="3"/>
-      <c r="DS48" s="21"/>
-      <c r="DT48" s="3"/>
-      <c r="DU48" s="3"/>
-      <c r="DV48" s="21"/>
-      <c r="DW48" s="1"/>
-      <c r="DX48" s="3"/>
-      <c r="DY48" s="3"/>
-      <c r="DZ48" s="3"/>
-      <c r="EA48" s="3"/>
-    </row>
-    <row r="49" spans="28:131" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AX48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY48" s="3"/>
+      <c r="AZ48" s="3"/>
+      <c r="BA48" s="3"/>
+      <c r="BB48" s="3"/>
+      <c r="BC48" s="3"/>
+      <c r="BD48" s="3"/>
+      <c r="BE48" s="3"/>
+      <c r="BF48" s="3"/>
+      <c r="BG48" s="19"/>
+      <c r="BH48" s="19"/>
+      <c r="BI48" s="3"/>
+      <c r="BJ48" s="3"/>
+      <c r="BK48" s="19"/>
+      <c r="BL48" s="3"/>
+      <c r="BM48" s="3"/>
+      <c r="BN48" s="3"/>
+      <c r="BO48" s="3"/>
+      <c r="BP48" s="3"/>
+      <c r="BQ48" s="3"/>
+      <c r="BR48" s="3"/>
+      <c r="BS48" s="26"/>
+      <c r="BT48" s="19"/>
+      <c r="BU48" s="26"/>
+      <c r="BV48" s="3"/>
+      <c r="BW48" s="19"/>
+      <c r="BX48" s="19"/>
+      <c r="BY48" s="26"/>
+      <c r="BZ48" s="3"/>
+    </row>
+    <row r="49" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB49" s="3"/>
-      <c r="AD49" s="23" t="s">
+      <c r="AD49" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="AE49" s="23"/>
-      <c r="AF49" s="23"/>
-      <c r="AG49" s="23"/>
-      <c r="AH49" s="23"/>
-      <c r="AI49" s="23"/>
-      <c r="AJ49" s="23"/>
-      <c r="AK49" s="23"/>
-      <c r="AL49" s="23"/>
-      <c r="AM49" s="23"/>
-      <c r="AN49" s="23"/>
-      <c r="AO49" s="23"/>
-      <c r="AP49" s="23"/>
-      <c r="AQ49" s="23"/>
-      <c r="CQ49" s="2" t="s">
+      <c r="AE49" s="24"/>
+      <c r="AF49" s="24"/>
+      <c r="AG49" s="24"/>
+      <c r="AH49" s="24"/>
+      <c r="AI49" s="24"/>
+      <c r="AJ49" s="24"/>
+      <c r="AK49" s="24"/>
+      <c r="AL49" s="24"/>
+      <c r="AM49" s="24"/>
+      <c r="AN49" s="24"/>
+      <c r="AO49" s="24"/>
+      <c r="AP49" s="24"/>
+      <c r="AQ49" s="24"/>
+      <c r="AX49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY49" s="20"/>
+      <c r="AZ49" s="20"/>
+      <c r="BA49" s="3"/>
+      <c r="BB49" s="10"/>
+      <c r="BC49" s="20"/>
+      <c r="BD49" s="20"/>
+      <c r="BE49" s="1"/>
+      <c r="BF49" s="10"/>
+      <c r="BG49" s="20"/>
+      <c r="BH49" s="20"/>
+      <c r="BI49" s="1"/>
+      <c r="BJ49" s="10"/>
+      <c r="BK49" s="20"/>
+      <c r="BL49" s="20"/>
+      <c r="BM49" s="1"/>
+      <c r="BN49" s="10"/>
+      <c r="BO49" s="20"/>
+      <c r="BP49" s="20"/>
+      <c r="BQ49" s="1"/>
+      <c r="BR49" s="10"/>
+      <c r="BS49" s="20"/>
+      <c r="BT49" s="20"/>
+      <c r="BU49" s="26"/>
+      <c r="BV49" s="10"/>
+      <c r="BW49" s="20"/>
+      <c r="BX49" s="20"/>
+      <c r="BY49" s="26"/>
+      <c r="BZ49" s="10"/>
+    </row>
+    <row r="50" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AX50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY50" s="3"/>
+      <c r="AZ50" s="3"/>
+      <c r="BA50" s="3"/>
+      <c r="BB50" s="3"/>
+      <c r="BC50" s="3"/>
+      <c r="BD50" s="19"/>
+      <c r="BE50" s="3"/>
+      <c r="BF50" s="3"/>
+      <c r="BG50" s="19"/>
+      <c r="BH50" s="19"/>
+      <c r="BI50" s="3"/>
+      <c r="BJ50" s="3"/>
+      <c r="BK50" s="3"/>
+      <c r="BL50" s="3"/>
+      <c r="BM50" s="3"/>
+      <c r="BN50" s="3"/>
+      <c r="BO50" s="3"/>
+      <c r="BP50" s="3"/>
+      <c r="BQ50" s="3"/>
+      <c r="BR50" s="3"/>
+      <c r="BS50" s="19"/>
+      <c r="BT50" s="19"/>
+      <c r="BU50" s="26"/>
+      <c r="BV50" s="3"/>
+      <c r="BW50" s="19"/>
+      <c r="BX50" s="26"/>
+      <c r="BY50" s="26"/>
+      <c r="BZ50" s="3"/>
+    </row>
+    <row r="51" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AX51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY51" s="20"/>
+      <c r="AZ51" s="20"/>
+      <c r="BA51" s="3"/>
+      <c r="BB51" s="10"/>
+      <c r="BC51" s="20"/>
+      <c r="BD51" s="20"/>
+      <c r="BE51" s="3"/>
+      <c r="BF51" s="10"/>
+      <c r="BG51" s="20"/>
+      <c r="BH51" s="20"/>
+      <c r="BI51" s="1"/>
+      <c r="BJ51" s="10"/>
+      <c r="BK51" s="20"/>
+      <c r="BL51" s="20"/>
+      <c r="BM51" s="1"/>
+      <c r="BN51" s="10"/>
+      <c r="BO51" s="20"/>
+      <c r="BP51" s="20"/>
+      <c r="BQ51" s="1"/>
+      <c r="BR51" s="10"/>
+      <c r="BS51" s="20"/>
+      <c r="BT51" s="20"/>
+      <c r="BU51" s="1"/>
+      <c r="BV51" s="10"/>
+      <c r="BW51" s="20"/>
+      <c r="BX51" s="20"/>
+      <c r="BY51" s="26"/>
+      <c r="BZ51" s="10"/>
+    </row>
+    <row r="52" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AX52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY52" s="3"/>
+      <c r="AZ52" s="3"/>
+      <c r="BA52" s="3"/>
+      <c r="BB52" s="3"/>
+      <c r="BC52" s="19"/>
+      <c r="BD52" s="19"/>
+      <c r="BE52" s="3"/>
+      <c r="BF52" s="3"/>
+      <c r="BG52" s="19"/>
+      <c r="BH52" s="3"/>
+      <c r="BI52" s="3"/>
+      <c r="BJ52" s="3"/>
+      <c r="BK52" s="3"/>
+      <c r="BL52" s="3"/>
+      <c r="BM52" s="3"/>
+      <c r="BN52" s="3"/>
+      <c r="BO52" s="3"/>
+      <c r="BP52" s="19"/>
+      <c r="BQ52" s="3"/>
+      <c r="BR52" s="3"/>
+      <c r="BS52" s="19"/>
+      <c r="BT52" s="19"/>
+      <c r="BU52" s="26"/>
+      <c r="BV52" s="3"/>
+      <c r="BW52" s="26"/>
+      <c r="BX52" s="26"/>
+      <c r="BY52" s="26"/>
+      <c r="BZ52" s="3"/>
+    </row>
+    <row r="53" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AX53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY53" s="20"/>
+      <c r="AZ53" s="20"/>
+      <c r="BA53" s="3"/>
+      <c r="BB53" s="10"/>
+      <c r="BC53" s="20"/>
+      <c r="BD53" s="20"/>
+      <c r="BE53" s="3"/>
+      <c r="BF53" s="10"/>
+      <c r="BG53" s="20"/>
+      <c r="BH53" s="20"/>
+      <c r="BI53" s="3"/>
+      <c r="BJ53" s="10"/>
+      <c r="BK53" s="20"/>
+      <c r="BL53" s="20"/>
+      <c r="BM53" s="1"/>
+      <c r="BN53" s="10"/>
+      <c r="BO53" s="20"/>
+      <c r="BP53" s="20"/>
+      <c r="BQ53" s="1"/>
+      <c r="BR53" s="10"/>
+      <c r="BS53" s="20"/>
+      <c r="BT53" s="20"/>
+      <c r="BU53" s="1"/>
+      <c r="BV53" s="10"/>
+      <c r="BW53" s="20"/>
+      <c r="BX53" s="20"/>
+      <c r="BY53" s="1"/>
+      <c r="BZ53" s="10"/>
+    </row>
+    <row r="54" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE54" s="2">
+        <v>7</v>
+      </c>
+      <c r="AF54" s="3"/>
+      <c r="AG54" s="3"/>
+      <c r="AH54" s="3"/>
+      <c r="AI54" s="3"/>
+      <c r="AJ54" s="19"/>
+      <c r="AK54" s="19"/>
+      <c r="AL54" s="19"/>
+      <c r="AN54" s="2">
+        <v>7</v>
+      </c>
+      <c r="AO54" s="1"/>
+      <c r="AP54" s="1"/>
+      <c r="AQ54" s="1"/>
+      <c r="AR54" s="1"/>
+      <c r="AS54" s="26"/>
+      <c r="AT54" s="26"/>
+      <c r="AU54" s="26"/>
+      <c r="AX54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY54" s="3"/>
+      <c r="AZ54" s="19"/>
+      <c r="BA54" s="3"/>
+      <c r="BB54" s="3"/>
+      <c r="BC54" s="19"/>
+      <c r="BD54" s="19"/>
+      <c r="BE54" s="3"/>
+      <c r="BF54" s="3"/>
+      <c r="BG54" s="3"/>
+      <c r="BH54" s="3"/>
+      <c r="BI54" s="3"/>
+      <c r="BJ54" s="3"/>
+      <c r="BK54" s="3"/>
+      <c r="BL54" s="3"/>
+      <c r="BM54" s="3"/>
+      <c r="BN54" s="3"/>
+      <c r="BO54" s="19"/>
+      <c r="BP54" s="19"/>
+      <c r="BQ54" s="3"/>
+      <c r="BR54" s="3"/>
+      <c r="BS54" s="19"/>
+      <c r="BT54" s="26"/>
+      <c r="BU54" s="26"/>
+      <c r="BV54" s="3"/>
+      <c r="BW54" s="26"/>
+      <c r="BX54" s="26"/>
+      <c r="BY54" s="26"/>
+      <c r="BZ54" s="3"/>
+    </row>
+    <row r="55" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE55" s="2">
+        <v>6</v>
+      </c>
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="19"/>
+      <c r="AJ55" s="19"/>
+      <c r="AK55" s="19"/>
+      <c r="AL55" s="3"/>
+      <c r="AN55" s="2">
+        <v>6</v>
+      </c>
+      <c r="AO55" s="26"/>
+      <c r="AP55" s="1"/>
+      <c r="AQ55" s="1"/>
+      <c r="AR55" s="1"/>
+      <c r="AS55" s="1"/>
+      <c r="AT55" s="26"/>
+      <c r="AU55" s="26"/>
+      <c r="AX55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY55" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="AZ55" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="BA55" s="1"/>
+      <c r="BB55" s="10"/>
+      <c r="BC55" s="20"/>
+      <c r="BD55" s="20"/>
+      <c r="BE55" s="3"/>
+      <c r="BF55" s="10"/>
+      <c r="BG55" s="20"/>
+      <c r="BH55" s="20"/>
+      <c r="BI55" s="3"/>
+      <c r="BJ55" s="10"/>
+      <c r="BK55" s="20"/>
+      <c r="BL55" s="20"/>
+      <c r="BM55" s="3"/>
+      <c r="BN55" s="10"/>
+      <c r="BO55" s="20"/>
+      <c r="BP55" s="20"/>
+      <c r="BQ55" s="1"/>
+      <c r="BR55" s="10"/>
+      <c r="BS55" s="20"/>
+      <c r="BT55" s="20"/>
+      <c r="BU55" s="1"/>
+      <c r="BV55" s="10"/>
+      <c r="BW55" s="20"/>
+      <c r="BX55" s="20"/>
+      <c r="BY55" s="1"/>
+      <c r="BZ55" s="10"/>
+    </row>
+    <row r="56" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE56" s="2">
+        <v>5</v>
+      </c>
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="19"/>
+      <c r="AI56" s="19"/>
+      <c r="AJ56" s="19"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AN56" s="2">
+        <v>5</v>
+      </c>
+      <c r="AO56" s="26"/>
+      <c r="AP56" s="26"/>
+      <c r="AQ56" s="1"/>
+      <c r="AR56" s="1"/>
+      <c r="AS56" s="1"/>
+      <c r="AT56" s="1"/>
+      <c r="AU56" s="26"/>
+      <c r="AX56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY56" s="19"/>
+      <c r="AZ56" s="19"/>
+      <c r="BA56" s="3"/>
+      <c r="BB56" s="3"/>
+      <c r="BC56" s="19"/>
+      <c r="BD56" s="3"/>
+      <c r="BE56" s="3"/>
+      <c r="BF56" s="3"/>
+      <c r="BG56" s="3"/>
+      <c r="BH56" s="3"/>
+      <c r="BI56" s="3"/>
+      <c r="BJ56" s="3"/>
+      <c r="BK56" s="3"/>
+      <c r="BL56" s="19"/>
+      <c r="BM56" s="3"/>
+      <c r="BN56" s="3"/>
+      <c r="BO56" s="19"/>
+      <c r="BP56" s="19"/>
+      <c r="BQ56" s="3"/>
+      <c r="BR56" s="3"/>
+      <c r="BS56" s="26"/>
+      <c r="BT56" s="26"/>
+      <c r="BU56" s="26"/>
+      <c r="BV56" s="3"/>
+      <c r="BW56" s="26"/>
+      <c r="BX56" s="26"/>
+      <c r="BY56" s="26"/>
+      <c r="BZ56" s="3"/>
+    </row>
+    <row r="57" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE57" s="2">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="3"/>
+      <c r="AG57" s="19"/>
+      <c r="AH57" s="19"/>
+      <c r="AI57" s="19"/>
+      <c r="AJ57" s="3"/>
+      <c r="AK57" s="3"/>
+      <c r="AL57" s="3"/>
+      <c r="AN57" s="2">
+        <v>4</v>
+      </c>
+      <c r="AO57" s="26"/>
+      <c r="AP57" s="26"/>
+      <c r="AQ57" s="26"/>
+      <c r="AR57" s="1"/>
+      <c r="AS57" s="1"/>
+      <c r="AT57" s="1"/>
+      <c r="AU57" s="1"/>
+      <c r="AX57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY57" s="20"/>
+      <c r="AZ57" s="20"/>
+      <c r="BA57" s="1"/>
+      <c r="BB57" s="10"/>
+      <c r="BC57" s="20"/>
+      <c r="BD57" s="20"/>
+      <c r="BE57" s="1"/>
+      <c r="BF57" s="10"/>
+      <c r="BG57" s="20"/>
+      <c r="BH57" s="20"/>
+      <c r="BI57" s="3"/>
+      <c r="BJ57" s="10"/>
+      <c r="BK57" s="20"/>
+      <c r="BL57" s="20"/>
+      <c r="BM57" s="3"/>
+      <c r="BN57" s="10"/>
+      <c r="BO57" s="20"/>
+      <c r="BP57" s="20"/>
+      <c r="BQ57" s="3"/>
+      <c r="BR57" s="10"/>
+      <c r="BS57" s="20"/>
+      <c r="BT57" s="20"/>
+      <c r="BU57" s="1"/>
+      <c r="BV57" s="10"/>
+      <c r="BW57" s="20"/>
+      <c r="BX57" s="20"/>
+      <c r="BY57" s="1"/>
+      <c r="BZ57" s="10"/>
+    </row>
+    <row r="58" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE58" s="2">
+        <v>3</v>
+      </c>
+      <c r="AF58" s="19"/>
+      <c r="AG58" s="19"/>
+      <c r="AH58" s="19"/>
+      <c r="AI58" s="3"/>
+      <c r="AJ58" s="3"/>
+      <c r="AK58" s="3"/>
+      <c r="AL58" s="3"/>
+      <c r="AN58" s="2">
+        <v>3</v>
+      </c>
+      <c r="AO58" s="1"/>
+      <c r="AP58" s="26"/>
+      <c r="AQ58" s="26"/>
+      <c r="AR58" s="26"/>
+      <c r="AS58" s="1"/>
+      <c r="AT58" s="1"/>
+      <c r="AU58" s="1"/>
+      <c r="AX58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY58" s="19"/>
+      <c r="AZ58" s="19"/>
+      <c r="BA58" s="3"/>
+      <c r="BB58" s="3"/>
+      <c r="BC58" s="3"/>
+      <c r="BD58" s="3"/>
+      <c r="BE58" s="3"/>
+      <c r="BF58" s="3"/>
+      <c r="BG58" s="3"/>
+      <c r="BH58" s="3"/>
+      <c r="BI58" s="3"/>
+      <c r="BJ58" s="3"/>
+      <c r="BK58" s="19"/>
+      <c r="BL58" s="19"/>
+      <c r="BM58" s="3"/>
+      <c r="BN58" s="3"/>
+      <c r="BO58" s="19"/>
+      <c r="BP58" s="3"/>
+      <c r="BQ58" s="3"/>
+      <c r="BR58" s="3"/>
+      <c r="BS58" s="26"/>
+      <c r="BT58" s="26"/>
+      <c r="BU58" s="26"/>
+      <c r="BV58" s="3"/>
+      <c r="BW58" s="26"/>
+      <c r="BX58" s="19"/>
+      <c r="BY58" s="26"/>
+      <c r="BZ58" s="3"/>
+    </row>
+    <row r="59" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE59" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF59" s="19"/>
+      <c r="AG59" s="19"/>
+      <c r="AH59" s="3"/>
+      <c r="AI59" s="3"/>
+      <c r="AJ59" s="3"/>
+      <c r="AK59" s="3"/>
+      <c r="AL59" s="19"/>
+      <c r="AN59" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO59" s="1"/>
+      <c r="AP59" s="1"/>
+      <c r="AQ59" s="26"/>
+      <c r="AR59" s="26"/>
+      <c r="AS59" s="26"/>
+      <c r="AT59" s="1"/>
+      <c r="AU59" s="1"/>
+      <c r="AX59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY59" s="20"/>
+      <c r="AZ59" s="20"/>
+      <c r="BA59" s="1"/>
+      <c r="BB59" s="10"/>
+      <c r="BC59" s="20"/>
+      <c r="BD59" s="20"/>
+      <c r="BE59" s="1"/>
+      <c r="BF59" s="10"/>
+      <c r="BG59" s="20"/>
+      <c r="BH59" s="20"/>
+      <c r="BI59" s="1"/>
+      <c r="BJ59" s="10"/>
+      <c r="BK59" s="20"/>
+      <c r="BL59" s="20"/>
+      <c r="BM59" s="3"/>
+      <c r="BN59" s="10"/>
+      <c r="BO59" s="20"/>
+      <c r="BP59" s="20"/>
+      <c r="BQ59" s="3"/>
+      <c r="BR59" s="10"/>
+      <c r="BS59" s="20"/>
+      <c r="BT59" s="20"/>
+      <c r="BU59" s="26"/>
+      <c r="BV59" s="10"/>
+      <c r="BW59" s="20"/>
+      <c r="BX59" s="20"/>
+      <c r="BY59" s="1"/>
+      <c r="BZ59" s="10"/>
+    </row>
+    <row r="60" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE60" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF60" s="19"/>
+      <c r="AG60" s="3"/>
+      <c r="AH60" s="3"/>
+      <c r="AI60" s="3"/>
+      <c r="AJ60" s="3"/>
+      <c r="AK60" s="19"/>
+      <c r="AL60" s="19"/>
+      <c r="AN60" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO60" s="1"/>
+      <c r="AP60" s="1"/>
+      <c r="AQ60" s="1"/>
+      <c r="AR60" s="26"/>
+      <c r="AS60" s="26"/>
+      <c r="AT60" s="26"/>
+      <c r="AU60" s="1"/>
+      <c r="AX60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY60" s="19"/>
+      <c r="AZ60" s="3"/>
+      <c r="BA60" s="3"/>
+      <c r="BB60" s="3"/>
+      <c r="BC60" s="3"/>
+      <c r="BD60" s="3"/>
+      <c r="BE60" s="3"/>
+      <c r="BF60" s="3"/>
+      <c r="BG60" s="3"/>
+      <c r="BH60" s="19"/>
+      <c r="BI60" s="3"/>
+      <c r="BJ60" s="3"/>
+      <c r="BK60" s="19"/>
+      <c r="BL60" s="19"/>
+      <c r="BM60" s="3"/>
+      <c r="BN60" s="3"/>
+      <c r="BO60" s="3"/>
+      <c r="BP60" s="3"/>
+      <c r="BQ60" s="3"/>
+      <c r="BR60" s="3"/>
+      <c r="BS60" s="26"/>
+      <c r="BT60" s="26"/>
+      <c r="BU60" s="26"/>
+      <c r="BV60" s="3"/>
+      <c r="BW60" s="19"/>
+      <c r="BX60" s="19"/>
+      <c r="BY60" s="26"/>
+      <c r="BZ60" s="3"/>
+    </row>
+    <row r="61" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE61" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="CR49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="CS49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="CT49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="CU49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="CV49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="CW49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="CX49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="CY49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="CZ49" s="2" t="s">
+      <c r="AF61" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG61" s="2">
+        <v>2</v>
+      </c>
+      <c r="AH61" s="2">
+        <v>3</v>
+      </c>
+      <c r="AI61" s="2">
+        <v>4</v>
+      </c>
+      <c r="AJ61" s="2">
+        <v>5</v>
+      </c>
+      <c r="AK61" s="2">
+        <v>6</v>
+      </c>
+      <c r="AL61" s="2">
+        <v>7</v>
+      </c>
+      <c r="AN61" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="2">
+        <v>1</v>
+      </c>
+      <c r="AP61" s="2">
+        <v>2</v>
+      </c>
+      <c r="AQ61" s="2">
+        <v>3</v>
+      </c>
+      <c r="AR61" s="2">
+        <v>4</v>
+      </c>
+      <c r="AS61" s="2">
+        <v>5</v>
+      </c>
+      <c r="AT61" s="2">
+        <v>6</v>
+      </c>
+      <c r="AU61" s="2">
+        <v>7</v>
+      </c>
+      <c r="AX61" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AY61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BB61" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="DA49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DB49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DC49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DD49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DE49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="DF49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="DG49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="DH49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="DI49" s="2" t="s">
+      <c r="BC61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BD61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BE61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BF61" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="DJ49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DK49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DL49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DM49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DN49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="DO49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="DP49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="DQ49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="DR49" s="2" t="s">
+      <c r="BG61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BI61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ61" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="DS49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DT49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DU49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DV49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="DW49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="DX49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="DY49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="DZ49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="EA49" s="2" t="s">
+      <c r="BK61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BL61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BM61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BN61" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="52" spans="28:131" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CZ52" s="21"/>
-      <c r="DB52" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="DC52" s="23"/>
-      <c r="DD52" s="23"/>
-      <c r="DE52" s="23"/>
-      <c r="DF52" s="23"/>
-      <c r="DG52" s="23"/>
-      <c r="DH52" s="23"/>
-      <c r="DI52" s="23"/>
-      <c r="DJ52" s="23"/>
-      <c r="DK52" s="23"/>
-      <c r="DL52" s="23"/>
-      <c r="DM52" s="23"/>
-      <c r="DN52" s="23"/>
-      <c r="DO52" s="23"/>
-    </row>
-    <row r="54" spans="28:131" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CZ54" s="1"/>
-      <c r="DB54" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="DC54" s="23"/>
-      <c r="DD54" s="23"/>
-      <c r="DE54" s="23"/>
-      <c r="DF54" s="23"/>
-      <c r="DG54" s="23"/>
-      <c r="DH54" s="23"/>
-      <c r="DI54" s="23"/>
-      <c r="DJ54" s="23"/>
-      <c r="DK54" s="23"/>
-      <c r="DL54" s="23"/>
-      <c r="DM54" s="23"/>
-      <c r="DN54" s="23"/>
-      <c r="DO54" s="23"/>
-    </row>
-    <row r="56" spans="28:131" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CZ56" s="20"/>
-      <c r="DB56" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="DC56" s="23"/>
-      <c r="DD56" s="23"/>
-      <c r="DE56" s="23"/>
-      <c r="DF56" s="23"/>
-      <c r="DG56" s="23"/>
-      <c r="DH56" s="23"/>
-      <c r="DI56" s="23"/>
-      <c r="DJ56" s="23"/>
-      <c r="DK56" s="23"/>
-      <c r="DL56" s="23"/>
-      <c r="DM56" s="23"/>
-      <c r="DN56" s="23"/>
-      <c r="DO56" s="23"/>
-    </row>
-    <row r="58" spans="28:131" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CZ58" s="22"/>
-      <c r="DB58" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="DC58" s="23"/>
-      <c r="DD58" s="23"/>
-      <c r="DE58" s="23"/>
-      <c r="DF58" s="23"/>
-      <c r="DG58" s="23"/>
-      <c r="DH58" s="23"/>
-      <c r="DI58" s="23"/>
-      <c r="DJ58" s="23"/>
-      <c r="DK58" s="23"/>
-      <c r="DL58" s="23"/>
-      <c r="DM58" s="23"/>
-      <c r="DN58" s="23"/>
-      <c r="DO58" s="23"/>
-    </row>
-    <row r="60" spans="28:131" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CZ60" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="DB60" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="DC60" s="23"/>
-      <c r="DD60" s="23"/>
-      <c r="DE60" s="23"/>
-      <c r="DF60" s="23"/>
-      <c r="DG60" s="23"/>
-      <c r="DH60" s="23"/>
-      <c r="DI60" s="23"/>
-      <c r="DJ60" s="23"/>
-      <c r="DK60" s="23"/>
-      <c r="DL60" s="23"/>
-      <c r="DM60" s="23"/>
-      <c r="DN60" s="23"/>
-      <c r="DO60" s="23"/>
-    </row>
-    <row r="62" spans="28:131" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CZ62" s="3"/>
-      <c r="DB62" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="DC62" s="23"/>
-      <c r="DD62" s="23"/>
-      <c r="DE62" s="23"/>
-      <c r="DF62" s="23"/>
-      <c r="DG62" s="23"/>
-      <c r="DH62" s="23"/>
-      <c r="DI62" s="23"/>
-      <c r="DJ62" s="23"/>
-      <c r="DK62" s="23"/>
-      <c r="DL62" s="23"/>
-      <c r="DM62" s="23"/>
-      <c r="DN62" s="23"/>
-      <c r="DO62" s="23"/>
+      <c r="BO61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BP61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BQ61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BR61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BS61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BT61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BU61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BV61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BW61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BX61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BY61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BZ61" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="28:78" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AG63" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH63" s="25"/>
+      <c r="AI63" s="25"/>
+      <c r="AP63" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ63" s="25"/>
+      <c r="AR63" s="25"/>
+      <c r="AS63" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="DB62:DO62"/>
-    <mergeCell ref="DB52:DO52"/>
-    <mergeCell ref="DB54:DO54"/>
-    <mergeCell ref="DB56:DO56"/>
-    <mergeCell ref="DB58:DO58"/>
-    <mergeCell ref="DB60:DO60"/>
+  <mergeCells count="10">
+    <mergeCell ref="AG63:AI63"/>
+    <mergeCell ref="AP63:AS63"/>
     <mergeCell ref="AD49:AQ49"/>
     <mergeCell ref="AD43:AQ43"/>
     <mergeCell ref="I37:L37"/>
@@ -9293,20 +10555,20 @@
       <c r="AZ28" s="3"/>
     </row>
     <row r="29" spans="4:52" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F29" s="23" t="s">
+      <c r="F29" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="O29" s="23" t="s">
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="O29" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="23"/>
-      <c r="S29" s="23"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="24"/>
+      <c r="R29" s="24"/>
+      <c r="S29" s="24"/>
       <c r="W29" s="2" t="s">
         <v>28</v>
       </c>
@@ -9780,22 +11042,22 @@
     </row>
     <row r="44" spans="23:69" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y44" s="17"/>
-      <c r="AA44" s="23" t="s">
+      <c r="AA44" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="AB44" s="23"/>
-      <c r="AC44" s="23"/>
-      <c r="AD44" s="23"/>
-      <c r="AE44" s="23"/>
-      <c r="AF44" s="23"/>
-      <c r="AG44" s="23"/>
-      <c r="AH44" s="23"/>
-      <c r="AI44" s="23"/>
-      <c r="AJ44" s="23"/>
-      <c r="AK44" s="23"/>
-      <c r="AL44" s="23"/>
-      <c r="AM44" s="23"/>
-      <c r="AN44" s="23"/>
+      <c r="AB44" s="24"/>
+      <c r="AC44" s="24"/>
+      <c r="AD44" s="24"/>
+      <c r="AE44" s="24"/>
+      <c r="AF44" s="24"/>
+      <c r="AG44" s="24"/>
+      <c r="AH44" s="24"/>
+      <c r="AI44" s="24"/>
+      <c r="AJ44" s="24"/>
+      <c r="AK44" s="24"/>
+      <c r="AL44" s="24"/>
+      <c r="AM44" s="24"/>
+      <c r="AN44" s="24"/>
       <c r="BJ44" s="15"/>
     </row>
     <row r="45" spans="23:69" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -9805,22 +11067,22 @@
     </row>
     <row r="46" spans="23:69" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y46" s="5"/>
-      <c r="AA46" s="23" t="s">
+      <c r="AA46" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="AB46" s="23"/>
-      <c r="AC46" s="23"/>
-      <c r="AD46" s="23"/>
-      <c r="AE46" s="23"/>
-      <c r="AF46" s="23"/>
-      <c r="AG46" s="23"/>
-      <c r="AH46" s="23"/>
-      <c r="AI46" s="23"/>
-      <c r="AJ46" s="23"/>
-      <c r="AK46" s="23"/>
-      <c r="AL46" s="23"/>
-      <c r="AM46" s="23"/>
-      <c r="AN46" s="23"/>
+      <c r="AB46" s="24"/>
+      <c r="AC46" s="24"/>
+      <c r="AD46" s="24"/>
+      <c r="AE46" s="24"/>
+      <c r="AF46" s="24"/>
+      <c r="AG46" s="24"/>
+      <c r="AH46" s="24"/>
+      <c r="AI46" s="24"/>
+      <c r="AJ46" s="24"/>
+      <c r="AK46" s="24"/>
+      <c r="AL46" s="24"/>
+      <c r="AM46" s="24"/>
+      <c r="AN46" s="24"/>
       <c r="BI46" s="15"/>
     </row>
     <row r="47" spans="23:69" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -9830,22 +11092,22 @@
     </row>
     <row r="48" spans="23:69" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y48" s="1"/>
-      <c r="AA48" s="23" t="s">
+      <c r="AA48" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="AB48" s="23"/>
-      <c r="AC48" s="23"/>
-      <c r="AD48" s="23"/>
-      <c r="AE48" s="23"/>
-      <c r="AF48" s="23"/>
-      <c r="AG48" s="23"/>
-      <c r="AH48" s="23"/>
-      <c r="AI48" s="23"/>
-      <c r="AJ48" s="23"/>
-      <c r="AK48" s="23"/>
-      <c r="AL48" s="23"/>
-      <c r="AM48" s="23"/>
-      <c r="AN48" s="23"/>
+      <c r="AB48" s="24"/>
+      <c r="AC48" s="24"/>
+      <c r="AD48" s="24"/>
+      <c r="AE48" s="24"/>
+      <c r="AF48" s="24"/>
+      <c r="AG48" s="24"/>
+      <c r="AH48" s="24"/>
+      <c r="AI48" s="24"/>
+      <c r="AJ48" s="24"/>
+      <c r="AK48" s="24"/>
+      <c r="AL48" s="24"/>
+      <c r="AM48" s="24"/>
+      <c r="AN48" s="24"/>
       <c r="AQ48" s="15"/>
       <c r="AX48" s="15"/>
       <c r="BF48" s="15"/>
@@ -9853,22 +11115,22 @@
     </row>
     <row r="50" spans="9:67" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y50" s="10"/>
-      <c r="AA50" s="23" t="s">
+      <c r="AA50" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AB50" s="23"/>
-      <c r="AC50" s="23"/>
-      <c r="AD50" s="23"/>
-      <c r="AE50" s="23"/>
-      <c r="AF50" s="23"/>
-      <c r="AG50" s="23"/>
-      <c r="AH50" s="23"/>
-      <c r="AI50" s="23"/>
-      <c r="AJ50" s="23"/>
-      <c r="AK50" s="23"/>
-      <c r="AL50" s="23"/>
-      <c r="AM50" s="23"/>
-      <c r="AN50" s="23"/>
+      <c r="AB50" s="24"/>
+      <c r="AC50" s="24"/>
+      <c r="AD50" s="24"/>
+      <c r="AE50" s="24"/>
+      <c r="AF50" s="24"/>
+      <c r="AG50" s="24"/>
+      <c r="AH50" s="24"/>
+      <c r="AI50" s="24"/>
+      <c r="AJ50" s="24"/>
+      <c r="AK50" s="24"/>
+      <c r="AL50" s="24"/>
+      <c r="AM50" s="24"/>
+      <c r="AN50" s="24"/>
       <c r="AO50" s="15"/>
       <c r="AU50" s="15"/>
       <c r="BM50" s="15"/>
@@ -9881,22 +11143,22 @@
       <c r="Y52" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AA52" s="23" t="s">
+      <c r="AA52" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="AB52" s="23"/>
-      <c r="AC52" s="23"/>
-      <c r="AD52" s="23"/>
-      <c r="AE52" s="23"/>
-      <c r="AF52" s="23"/>
-      <c r="AG52" s="23"/>
-      <c r="AH52" s="23"/>
-      <c r="AI52" s="23"/>
-      <c r="AJ52" s="23"/>
-      <c r="AK52" s="23"/>
-      <c r="AL52" s="23"/>
-      <c r="AM52" s="23"/>
-      <c r="AN52" s="23"/>
+      <c r="AB52" s="24"/>
+      <c r="AC52" s="24"/>
+      <c r="AD52" s="24"/>
+      <c r="AE52" s="24"/>
+      <c r="AF52" s="24"/>
+      <c r="AG52" s="24"/>
+      <c r="AH52" s="24"/>
+      <c r="AI52" s="24"/>
+      <c r="AJ52" s="24"/>
+      <c r="AK52" s="24"/>
+      <c r="AL52" s="24"/>
+      <c r="AM52" s="24"/>
+      <c r="AN52" s="24"/>
       <c r="AR52" s="15"/>
       <c r="BN52" s="15"/>
     </row>
@@ -9910,22 +11172,22 @@
       <c r="U54" s="16"/>
       <c r="V54" s="16"/>
       <c r="Y54" s="3"/>
-      <c r="AA54" s="23" t="s">
+      <c r="AA54" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="AB54" s="23"/>
-      <c r="AC54" s="23"/>
-      <c r="AD54" s="23"/>
-      <c r="AE54" s="23"/>
-      <c r="AF54" s="23"/>
-      <c r="AG54" s="23"/>
-      <c r="AH54" s="23"/>
-      <c r="AI54" s="23"/>
-      <c r="AJ54" s="23"/>
-      <c r="AK54" s="23"/>
-      <c r="AL54" s="23"/>
-      <c r="AM54" s="23"/>
-      <c r="AN54" s="23"/>
+      <c r="AB54" s="24"/>
+      <c r="AC54" s="24"/>
+      <c r="AD54" s="24"/>
+      <c r="AE54" s="24"/>
+      <c r="AF54" s="24"/>
+      <c r="AG54" s="24"/>
+      <c r="AH54" s="24"/>
+      <c r="AI54" s="24"/>
+      <c r="AJ54" s="24"/>
+      <c r="AK54" s="24"/>
+      <c r="AL54" s="24"/>
+      <c r="AM54" s="24"/>
+      <c r="AN54" s="24"/>
     </row>
     <row r="56" spans="9:67" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AD56" s="16"/>
@@ -10650,20 +11912,20 @@
       <c r="AU27" s="17"/>
     </row>
     <row r="28" spans="7:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H28" s="23" t="s">
+      <c r="H28" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="O28" s="23" t="s">
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="O28" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="24"/>
       <c r="V28" s="2" t="s">
         <v>9</v>
       </c>
@@ -10735,60 +11997,60 @@
     </row>
     <row r="32" spans="7:47" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y32" s="1"/>
-      <c r="AA32" s="23" t="s">
+      <c r="AA32" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="AB32" s="23"/>
-      <c r="AC32" s="23"/>
-      <c r="AD32" s="23"/>
-      <c r="AE32" s="23"/>
-      <c r="AF32" s="23"/>
-      <c r="AG32" s="23"/>
-      <c r="AH32" s="23"/>
-      <c r="AI32" s="23"/>
-      <c r="AJ32" s="23"/>
-      <c r="AK32" s="23"/>
-      <c r="AL32" s="23"/>
-      <c r="AM32" s="23"/>
-      <c r="AN32" s="23"/>
+      <c r="AB32" s="24"/>
+      <c r="AC32" s="24"/>
+      <c r="AD32" s="24"/>
+      <c r="AE32" s="24"/>
+      <c r="AF32" s="24"/>
+      <c r="AG32" s="24"/>
+      <c r="AH32" s="24"/>
+      <c r="AI32" s="24"/>
+      <c r="AJ32" s="24"/>
+      <c r="AK32" s="24"/>
+      <c r="AL32" s="24"/>
+      <c r="AM32" s="24"/>
+      <c r="AN32" s="24"/>
     </row>
     <row r="34" spans="6:52" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y34" s="19"/>
-      <c r="AA34" s="23" t="s">
+      <c r="AA34" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="AB34" s="23"/>
-      <c r="AC34" s="23"/>
-      <c r="AD34" s="23"/>
-      <c r="AE34" s="23"/>
-      <c r="AF34" s="23"/>
-      <c r="AG34" s="23"/>
-      <c r="AH34" s="23"/>
-      <c r="AI34" s="23"/>
-      <c r="AJ34" s="23"/>
-      <c r="AK34" s="23"/>
-      <c r="AL34" s="23"/>
-      <c r="AM34" s="23"/>
-      <c r="AN34" s="23"/>
+      <c r="AB34" s="24"/>
+      <c r="AC34" s="24"/>
+      <c r="AD34" s="24"/>
+      <c r="AE34" s="24"/>
+      <c r="AF34" s="24"/>
+      <c r="AG34" s="24"/>
+      <c r="AH34" s="24"/>
+      <c r="AI34" s="24"/>
+      <c r="AJ34" s="24"/>
+      <c r="AK34" s="24"/>
+      <c r="AL34" s="24"/>
+      <c r="AM34" s="24"/>
+      <c r="AN34" s="24"/>
     </row>
     <row r="36" spans="6:52" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y36" s="17"/>
-      <c r="AA36" s="23" t="s">
+      <c r="AA36" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AB36" s="23"/>
-      <c r="AC36" s="23"/>
-      <c r="AD36" s="23"/>
-      <c r="AE36" s="23"/>
-      <c r="AF36" s="23"/>
-      <c r="AG36" s="23"/>
-      <c r="AH36" s="23"/>
-      <c r="AI36" s="23"/>
-      <c r="AJ36" s="23"/>
-      <c r="AK36" s="23"/>
-      <c r="AL36" s="23"/>
-      <c r="AM36" s="23"/>
-      <c r="AN36" s="23"/>
+      <c r="AB36" s="24"/>
+      <c r="AC36" s="24"/>
+      <c r="AD36" s="24"/>
+      <c r="AE36" s="24"/>
+      <c r="AF36" s="24"/>
+      <c r="AG36" s="24"/>
+      <c r="AH36" s="24"/>
+      <c r="AI36" s="24"/>
+      <c r="AJ36" s="24"/>
+      <c r="AK36" s="24"/>
+      <c r="AL36" s="24"/>
+      <c r="AM36" s="24"/>
+      <c r="AN36" s="24"/>
     </row>
     <row r="37" spans="6:52" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AU37" s="15"/>
@@ -10797,22 +12059,22 @@
       <c r="Y38" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AA38" s="23" t="s">
+      <c r="AA38" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="AB38" s="23"/>
-      <c r="AC38" s="23"/>
-      <c r="AD38" s="23"/>
-      <c r="AE38" s="23"/>
-      <c r="AF38" s="23"/>
-      <c r="AG38" s="23"/>
-      <c r="AH38" s="23"/>
-      <c r="AI38" s="23"/>
-      <c r="AJ38" s="23"/>
-      <c r="AK38" s="23"/>
-      <c r="AL38" s="23"/>
-      <c r="AM38" s="23"/>
-      <c r="AN38" s="23"/>
+      <c r="AB38" s="24"/>
+      <c r="AC38" s="24"/>
+      <c r="AD38" s="24"/>
+      <c r="AE38" s="24"/>
+      <c r="AF38" s="24"/>
+      <c r="AG38" s="24"/>
+      <c r="AH38" s="24"/>
+      <c r="AI38" s="24"/>
+      <c r="AJ38" s="24"/>
+      <c r="AK38" s="24"/>
+      <c r="AL38" s="24"/>
+      <c r="AM38" s="24"/>
+      <c r="AN38" s="24"/>
       <c r="AP38" s="15"/>
       <c r="AS38" s="15"/>
       <c r="AX38" s="15"/>
@@ -10827,44 +12089,44 @@
       <c r="Y40" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AA40" s="23" t="s">
+      <c r="AA40" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="AB40" s="23"/>
-      <c r="AC40" s="23"/>
-      <c r="AD40" s="23"/>
-      <c r="AE40" s="23"/>
-      <c r="AF40" s="23"/>
-      <c r="AG40" s="23"/>
-      <c r="AH40" s="23"/>
-      <c r="AI40" s="23"/>
-      <c r="AJ40" s="23"/>
-      <c r="AK40" s="23"/>
-      <c r="AL40" s="23"/>
-      <c r="AM40" s="23"/>
-      <c r="AN40" s="23"/>
+      <c r="AB40" s="24"/>
+      <c r="AC40" s="24"/>
+      <c r="AD40" s="24"/>
+      <c r="AE40" s="24"/>
+      <c r="AF40" s="24"/>
+      <c r="AG40" s="24"/>
+      <c r="AH40" s="24"/>
+      <c r="AI40" s="24"/>
+      <c r="AJ40" s="24"/>
+      <c r="AK40" s="24"/>
+      <c r="AL40" s="24"/>
+      <c r="AM40" s="24"/>
+      <c r="AN40" s="24"/>
       <c r="AP40" s="15"/>
       <c r="AS40" s="15"/>
       <c r="AX40" s="15"/>
     </row>
     <row r="42" spans="6:52" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y42" s="3"/>
-      <c r="AA42" s="23" t="s">
+      <c r="AA42" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="AB42" s="23"/>
-      <c r="AC42" s="23"/>
-      <c r="AD42" s="23"/>
-      <c r="AE42" s="23"/>
-      <c r="AF42" s="23"/>
-      <c r="AG42" s="23"/>
-      <c r="AH42" s="23"/>
-      <c r="AI42" s="23"/>
-      <c r="AJ42" s="23"/>
-      <c r="AK42" s="23"/>
-      <c r="AL42" s="23"/>
-      <c r="AM42" s="23"/>
-      <c r="AN42" s="23"/>
+      <c r="AB42" s="24"/>
+      <c r="AC42" s="24"/>
+      <c r="AD42" s="24"/>
+      <c r="AE42" s="24"/>
+      <c r="AF42" s="24"/>
+      <c r="AG42" s="24"/>
+      <c r="AH42" s="24"/>
+      <c r="AI42" s="24"/>
+      <c r="AJ42" s="24"/>
+      <c r="AK42" s="24"/>
+      <c r="AL42" s="24"/>
+      <c r="AM42" s="24"/>
+      <c r="AN42" s="24"/>
       <c r="AY42" s="15"/>
     </row>
     <row r="43" spans="6:52" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -11975,79 +13237,79 @@
       </c>
     </row>
     <row r="33" spans="8:51" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H33" s="23" t="s">
+      <c r="H33" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="P33" s="23" t="s">
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+      <c r="P33" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="23"/>
-      <c r="S33" s="23"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="23"/>
+      <c r="Q33" s="24"/>
+      <c r="R33" s="24"/>
+      <c r="S33" s="24"/>
+      <c r="T33" s="24"/>
+      <c r="U33" s="24"/>
     </row>
     <row r="37" spans="8:51" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y37" s="1"/>
-      <c r="AA37" s="23" t="s">
+      <c r="AA37" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="AB37" s="23"/>
-      <c r="AC37" s="23"/>
-      <c r="AD37" s="23"/>
-      <c r="AE37" s="23"/>
-      <c r="AF37" s="23"/>
-      <c r="AG37" s="23"/>
-      <c r="AH37" s="23"/>
-      <c r="AI37" s="23"/>
-      <c r="AJ37" s="23"/>
-      <c r="AK37" s="23"/>
-      <c r="AL37" s="23"/>
-      <c r="AM37" s="23"/>
-      <c r="AN37" s="23"/>
+      <c r="AB37" s="24"/>
+      <c r="AC37" s="24"/>
+      <c r="AD37" s="24"/>
+      <c r="AE37" s="24"/>
+      <c r="AF37" s="24"/>
+      <c r="AG37" s="24"/>
+      <c r="AH37" s="24"/>
+      <c r="AI37" s="24"/>
+      <c r="AJ37" s="24"/>
+      <c r="AK37" s="24"/>
+      <c r="AL37" s="24"/>
+      <c r="AM37" s="24"/>
+      <c r="AN37" s="24"/>
     </row>
     <row r="39" spans="8:51" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y39" s="19"/>
-      <c r="AA39" s="23" t="s">
+      <c r="AA39" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="AB39" s="23"/>
-      <c r="AC39" s="23"/>
-      <c r="AD39" s="23"/>
-      <c r="AE39" s="23"/>
-      <c r="AF39" s="23"/>
-      <c r="AG39" s="23"/>
-      <c r="AH39" s="23"/>
-      <c r="AI39" s="23"/>
-      <c r="AJ39" s="23"/>
-      <c r="AK39" s="23"/>
-      <c r="AL39" s="23"/>
-      <c r="AM39" s="23"/>
-      <c r="AN39" s="23"/>
+      <c r="AB39" s="24"/>
+      <c r="AC39" s="24"/>
+      <c r="AD39" s="24"/>
+      <c r="AE39" s="24"/>
+      <c r="AF39" s="24"/>
+      <c r="AG39" s="24"/>
+      <c r="AH39" s="24"/>
+      <c r="AI39" s="24"/>
+      <c r="AJ39" s="24"/>
+      <c r="AK39" s="24"/>
+      <c r="AL39" s="24"/>
+      <c r="AM39" s="24"/>
+      <c r="AN39" s="24"/>
     </row>
     <row r="41" spans="8:51" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y41" s="17"/>
-      <c r="AA41" s="23" t="s">
+      <c r="AA41" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AB41" s="23"/>
-      <c r="AC41" s="23"/>
-      <c r="AD41" s="23"/>
-      <c r="AE41" s="23"/>
-      <c r="AF41" s="23"/>
-      <c r="AG41" s="23"/>
-      <c r="AH41" s="23"/>
-      <c r="AI41" s="23"/>
-      <c r="AJ41" s="23"/>
-      <c r="AK41" s="23"/>
-      <c r="AL41" s="23"/>
-      <c r="AM41" s="23"/>
-      <c r="AN41" s="23"/>
+      <c r="AB41" s="24"/>
+      <c r="AC41" s="24"/>
+      <c r="AD41" s="24"/>
+      <c r="AE41" s="24"/>
+      <c r="AF41" s="24"/>
+      <c r="AG41" s="24"/>
+      <c r="AH41" s="24"/>
+      <c r="AI41" s="24"/>
+      <c r="AJ41" s="24"/>
+      <c r="AK41" s="24"/>
+      <c r="AL41" s="24"/>
+      <c r="AM41" s="24"/>
+      <c r="AN41" s="24"/>
     </row>
     <row r="42" spans="8:51" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AU42" s="15"/>
@@ -12056,22 +13318,22 @@
       <c r="Y43" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AA43" s="23" t="s">
+      <c r="AA43" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="AB43" s="23"/>
-      <c r="AC43" s="23"/>
-      <c r="AD43" s="23"/>
-      <c r="AE43" s="23"/>
-      <c r="AF43" s="23"/>
-      <c r="AG43" s="23"/>
-      <c r="AH43" s="23"/>
-      <c r="AI43" s="23"/>
-      <c r="AJ43" s="23"/>
-      <c r="AK43" s="23"/>
-      <c r="AL43" s="23"/>
-      <c r="AM43" s="23"/>
-      <c r="AN43" s="23"/>
+      <c r="AB43" s="24"/>
+      <c r="AC43" s="24"/>
+      <c r="AD43" s="24"/>
+      <c r="AE43" s="24"/>
+      <c r="AF43" s="24"/>
+      <c r="AG43" s="24"/>
+      <c r="AH43" s="24"/>
+      <c r="AI43" s="24"/>
+      <c r="AJ43" s="24"/>
+      <c r="AK43" s="24"/>
+      <c r="AL43" s="24"/>
+      <c r="AM43" s="24"/>
+      <c r="AN43" s="24"/>
       <c r="AP43" s="15"/>
       <c r="AS43" s="15"/>
       <c r="AX43" s="15"/>
@@ -12086,44 +13348,44 @@
       <c r="Y45" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AA45" s="23" t="s">
+      <c r="AA45" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="AB45" s="23"/>
-      <c r="AC45" s="23"/>
-      <c r="AD45" s="23"/>
-      <c r="AE45" s="23"/>
-      <c r="AF45" s="23"/>
-      <c r="AG45" s="23"/>
-      <c r="AH45" s="23"/>
-      <c r="AI45" s="23"/>
-      <c r="AJ45" s="23"/>
-      <c r="AK45" s="23"/>
-      <c r="AL45" s="23"/>
-      <c r="AM45" s="23"/>
-      <c r="AN45" s="23"/>
+      <c r="AB45" s="24"/>
+      <c r="AC45" s="24"/>
+      <c r="AD45" s="24"/>
+      <c r="AE45" s="24"/>
+      <c r="AF45" s="24"/>
+      <c r="AG45" s="24"/>
+      <c r="AH45" s="24"/>
+      <c r="AI45" s="24"/>
+      <c r="AJ45" s="24"/>
+      <c r="AK45" s="24"/>
+      <c r="AL45" s="24"/>
+      <c r="AM45" s="24"/>
+      <c r="AN45" s="24"/>
       <c r="AP45" s="15"/>
       <c r="AS45" s="15"/>
       <c r="AX45" s="15"/>
     </row>
     <row r="47" spans="8:51" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y47" s="3"/>
-      <c r="AA47" s="23" t="s">
+      <c r="AA47" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="AB47" s="23"/>
-      <c r="AC47" s="23"/>
-      <c r="AD47" s="23"/>
-      <c r="AE47" s="23"/>
-      <c r="AF47" s="23"/>
-      <c r="AG47" s="23"/>
-      <c r="AH47" s="23"/>
-      <c r="AI47" s="23"/>
-      <c r="AJ47" s="23"/>
-      <c r="AK47" s="23"/>
-      <c r="AL47" s="23"/>
-      <c r="AM47" s="23"/>
-      <c r="AN47" s="23"/>
+      <c r="AB47" s="24"/>
+      <c r="AC47" s="24"/>
+      <c r="AD47" s="24"/>
+      <c r="AE47" s="24"/>
+      <c r="AF47" s="24"/>
+      <c r="AG47" s="24"/>
+      <c r="AH47" s="24"/>
+      <c r="AI47" s="24"/>
+      <c r="AJ47" s="24"/>
+      <c r="AK47" s="24"/>
+      <c r="AL47" s="24"/>
+      <c r="AM47" s="24"/>
+      <c r="AN47" s="24"/>
       <c r="AY47" s="15"/>
     </row>
     <row r="48" spans="8:51" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
